--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -251,6 +251,18 @@
   </x:si>
   <x:si>
     <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
   </x:si>
   <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
@@ -649,7 +661,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K126"/>
+  <x:dimension ref="A1:K136"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1147,10 +1159,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>80.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>1.06</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>39</x:v>
@@ -1777,10 +1789,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>23.22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>-2.11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
         <x:v>73</x:v>
@@ -1877,48 +1889,84 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" spans="1:11">
+      <x:c r="A36" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I36" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J36" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K36" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:11">
-      <x:c r="A38" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C38" s="0" t="s">
+      <x:c r="E37" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>4</x:v>
+      <x:c r="F37" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J37" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K37" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>84</x:v>
@@ -1927,78 +1975,78 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
@@ -2009,10 +2057,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
         <x:v>21</x:v>
@@ -2020,16 +2068,16 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
         <x:v>21</x:v>
@@ -2037,16 +2085,16 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
         <x:v>21</x:v>
@@ -2057,13 +2105,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
         <x:v>21</x:v>
@@ -2071,47 +2119,47 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>25</x:v>
@@ -2122,13 +2170,13 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>25</x:v>
@@ -2139,41 +2187,41 @@
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>88</x:v>
@@ -2190,13 +2238,13 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>29</x:v>
@@ -2210,10 +2258,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>29</x:v>
@@ -2227,10 +2275,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>29</x:v>
@@ -2244,10 +2292,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>29</x:v>
@@ -2261,10 +2309,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>29</x:v>
@@ -2275,16 +2323,16 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
         <x:v>30</x:v>
@@ -2292,16 +2340,16 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
         <x:v>30</x:v>
@@ -2309,13 +2357,13 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>33</x:v>
@@ -2326,13 +2374,13 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>33</x:v>
@@ -2343,13 +2391,13 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>33</x:v>
@@ -2360,13 +2408,13 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>33</x:v>
@@ -2377,16 +2425,16 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
         <x:v>30</x:v>
@@ -2394,16 +2442,16 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
         <x:v>30</x:v>
@@ -2411,47 +2459,47 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>39</x:v>
@@ -2462,13 +2510,13 @@
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>39</x:v>
@@ -2479,16 +2527,16 @@
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
         <x:v>40</x:v>
@@ -2496,16 +2544,16 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
         <x:v>40</x:v>
@@ -2513,13 +2561,13 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>43</x:v>
@@ -2530,13 +2578,13 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>43</x:v>
@@ -2547,13 +2595,13 @@
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>43</x:v>
@@ -2564,13 +2612,13 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>43</x:v>
@@ -2581,36 +2629,36 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
@@ -2618,10 +2666,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>47</x:v>
@@ -2635,10 +2683,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>47</x:v>
@@ -2652,10 +2700,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>47</x:v>
@@ -2669,10 +2717,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>47</x:v>
@@ -2683,16 +2731,16 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
         <x:v>48</x:v>
@@ -2700,16 +2748,16 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
         <x:v>48</x:v>
@@ -2720,10 +2768,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>50</x:v>
@@ -2737,10 +2785,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>50</x:v>
@@ -2754,10 +2802,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>50</x:v>
@@ -2771,10 +2819,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>50</x:v>
@@ -2785,13 +2833,13 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>50</x:v>
@@ -2802,13 +2850,13 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>50</x:v>
@@ -2819,13 +2867,13 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>50</x:v>
@@ -2836,13 +2884,13 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>50</x:v>
@@ -2853,16 +2901,16 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
         <x:v>48</x:v>
@@ -2870,16 +2918,16 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
         <x:v>48</x:v>
@@ -2890,10 +2938,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>54</x:v>
@@ -2910,7 +2958,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>54</x:v>
@@ -2944,7 +2992,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>54</x:v>
@@ -2955,36 +3003,36 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
@@ -2992,13 +3040,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
         <x:v>57</x:v>
@@ -3006,81 +3054,81 @@
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>62</x:v>
@@ -3091,13 +3139,13 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>62</x:v>
@@ -3108,36 +3156,36 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
@@ -3145,13 +3193,13 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
         <x:v>67</x:v>
@@ -3159,16 +3207,16 @@
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
         <x:v>67</x:v>
@@ -3176,13 +3224,13 @@
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>69</x:v>
@@ -3193,13 +3241,13 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>69</x:v>
@@ -3210,13 +3258,13 @@
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>69</x:v>
@@ -3227,13 +3275,13 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>69</x:v>
@@ -3244,13 +3292,13 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>69</x:v>
@@ -3261,16 +3309,16 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
         <x:v>67</x:v>
@@ -3278,16 +3326,16 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
         <x:v>67</x:v>
@@ -3295,13 +3343,13 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>73</x:v>
@@ -3312,13 +3360,13 @@
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>73</x:v>
@@ -3329,47 +3377,47 @@
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>76</x:v>
@@ -3380,19 +3428,189 @@
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
         <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:11">
+      <x:c r="A127" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:11">
+      <x:c r="A128" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E128" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:11">
+      <x:c r="A129" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E129" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:11">
+      <x:c r="A130" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E130" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:11">
+      <x:c r="A131" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E131" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:11">
+      <x:c r="A132" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E132" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:11">
+      <x:c r="A133" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E133" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:11">
+      <x:c r="A134" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E134" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:11">
+      <x:c r="A135" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E135" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:11">
+      <x:c r="A136" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D136" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E136" s="0" t="s">
+        <x:v>81</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -263,6 +263,21 @@
   </x:si>
   <x:si>
     <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
   </x:si>
   <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
@@ -661,7 +676,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K136"/>
+  <x:dimension ref="A1:K152"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1959,176 +1974,248 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="38" spans="1:11">
+      <x:c r="A38" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B38" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J38" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K38" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J39" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K39" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E40" s="0" t="s">
-        <x:v>4</x:v>
+      <x:c r="F40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K40" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
+      <x:c r="B41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:11">
-      <x:c r="A42" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K41" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
         <x:v>21</x:v>
@@ -2136,16 +2223,16 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
         <x:v>21</x:v>
@@ -2153,149 +2240,149 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>29</x:v>
@@ -2306,13 +2393,13 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>29</x:v>
@@ -2326,10 +2413,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>29</x:v>
@@ -2343,10 +2430,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>29</x:v>
@@ -2357,16 +2444,16 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
         <x:v>30</x:v>
@@ -2374,16 +2461,16 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
         <x:v>30</x:v>
@@ -2391,16 +2478,16 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
         <x:v>30</x:v>
@@ -2408,16 +2495,16 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
         <x:v>30</x:v>
@@ -2425,13 +2512,13 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>33</x:v>
@@ -2442,13 +2529,13 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>33</x:v>
@@ -2459,16 +2546,16 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
         <x:v>30</x:v>
@@ -2476,16 +2563,16 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
         <x:v>30</x:v>
@@ -2493,84 +2580,84 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
         <x:v>40</x:v>
@@ -2578,16 +2665,16 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
         <x:v>40</x:v>
@@ -2595,16 +2682,16 @@
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
         <x:v>40</x:v>
@@ -2612,16 +2699,16 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
         <x:v>40</x:v>
@@ -2629,13 +2716,13 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>43</x:v>
@@ -2646,13 +2733,13 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>43</x:v>
@@ -2663,70 +2750,70 @@
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C81" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C82" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
@@ -2734,10 +2821,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>47</x:v>
@@ -2751,10 +2838,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>47</x:v>
@@ -2765,16 +2852,16 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
         <x:v>48</x:v>
@@ -2782,16 +2869,16 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
         <x:v>48</x:v>
@@ -2799,16 +2886,16 @@
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
         <x:v>48</x:v>
@@ -2816,16 +2903,16 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
         <x:v>48</x:v>
@@ -2836,10 +2923,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>50</x:v>
@@ -2853,10 +2940,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>50</x:v>
@@ -2867,13 +2954,13 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>50</x:v>
@@ -2884,13 +2971,13 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>50</x:v>
@@ -2901,13 +2988,13 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>50</x:v>
@@ -2918,13 +3005,13 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>50</x:v>
@@ -2935,16 +3022,16 @@
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
         <x:v>48</x:v>
@@ -2952,16 +3039,16 @@
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
         <x:v>48</x:v>
@@ -2969,16 +3056,16 @@
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
         <x:v>48</x:v>
@@ -2986,16 +3073,16 @@
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
         <x:v>48</x:v>
@@ -3006,10 +3093,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>54</x:v>
@@ -3023,10 +3110,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
         <x:v>54</x:v>
@@ -3037,237 +3124,237 @@
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
         <x:v>67</x:v>
@@ -3275,16 +3362,16 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
         <x:v>67</x:v>
@@ -3292,13 +3379,13 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>69</x:v>
@@ -3309,13 +3396,13 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
         <x:v>69</x:v>
@@ -3326,13 +3413,13 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>69</x:v>
@@ -3343,16 +3430,16 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
         <x:v>67</x:v>
@@ -3360,16 +3447,16 @@
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
         <x:v>67</x:v>
@@ -3377,16 +3464,16 @@
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
         <x:v>67</x:v>
@@ -3394,16 +3481,16 @@
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
         <x:v>67</x:v>
@@ -3411,149 +3498,149 @@
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
         <x:v>80</x:v>
@@ -3564,13 +3651,13 @@
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>80</x:v>
@@ -3584,10 +3671,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
         <x:v>80</x:v>
@@ -3601,16 +3688,288 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
         <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:11">
+      <x:c r="A137" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E137" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:11">
+      <x:c r="A138" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D138" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E138" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:11">
+      <x:c r="A139" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E139" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:11">
+      <x:c r="A140" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E140" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:11">
+      <x:c r="A141" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D141" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E141" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:11">
+      <x:c r="A142" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D142" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E142" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:11">
+      <x:c r="A143" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D143" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E143" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:11">
+      <x:c r="A144" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D144" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E144" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:11">
+      <x:c r="A145" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E145" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:11">
+      <x:c r="A146" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D146" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E146" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:11">
+      <x:c r="A147" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D147" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E147" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:11">
+      <x:c r="A148" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D148" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E148" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:11">
+      <x:c r="A149" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E149" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:11">
+      <x:c r="A150" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E150" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:11">
+      <x:c r="A151" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D151" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E151" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:11">
+      <x:c r="A152" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D152" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E152" s="0" t="s">
+        <x:v>84</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,235 +49,232 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>TATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.03.2026</x:t>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
   </x:si>
   <x:si>
     <x:t>15.04.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
   </x:si>
   <x:si>
     <x:t>NIBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YIGIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
+    <x:t>15.05.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
@@ -307,16 +304,16 @@
     <x:t>18.03.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
     <x:t>PEIAK</x:t>
   </x:si>
   <x:si>
     <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
   <x:si>
     <x:t>PYAYN</x:t>
@@ -676,7 +673,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K152"/>
+  <x:dimension ref="A1:K150"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -766,7 +763,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>15</x:v>
@@ -798,7 +795,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>15</x:v>
@@ -821,22 +818,22 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="E5" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>15</x:v>
@@ -865,10 +862,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>14</x:v>
@@ -891,19 +888,19 @@
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B7" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="B7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>14</x:v>
@@ -935,13 +932,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
         <x:v>15</x:v>
@@ -950,18 +947,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -970,13 +967,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>15</x:v>
@@ -985,18 +982,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="0">
         <x:v>0</x:v>
@@ -1005,10 +1002,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>14</x:v>
@@ -1031,7 +1028,7 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="0">
         <x:v>0</x:v>
@@ -1040,10 +1037,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>14</x:v>
@@ -1066,7 +1063,7 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="0">
         <x:v>0</x:v>
@@ -1075,10 +1072,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>14</x:v>
@@ -1101,19 +1098,19 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
+      <x:c r="E13" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>14</x:v>
@@ -1145,10 +1142,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>14</x:v>
@@ -1171,7 +1168,7 @@
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="0">
         <x:v>0</x:v>
@@ -1180,10 +1177,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>14</x:v>
@@ -1206,7 +1203,7 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="0">
         <x:v>0</x:v>
@@ -1215,10 +1212,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>14</x:v>
@@ -1241,7 +1238,7 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1250,10 +1247,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>14</x:v>
@@ -1276,22 +1273,22 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>15</x:v>
@@ -1300,13 +1297,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
@@ -1323,7 +1320,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>15</x:v>
@@ -1346,7 +1343,7 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="0">
         <x:v>0</x:v>
@@ -1355,13 +1352,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
         <x:v>15</x:v>
@@ -1370,18 +1367,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B21" s="0">
         <x:v>0</x:v>
@@ -1390,10 +1387,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>14</x:v>
@@ -1416,7 +1413,7 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B22" s="0">
         <x:v>0</x:v>
@@ -1425,13 +1422,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
         <x:v>15</x:v>
@@ -1440,31 +1437,31 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
+      <x:c r="E23" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1475,13 +1472,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -1501,7 +1498,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
         <x:v>15</x:v>
@@ -1571,7 +1568,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
         <x:v>15</x:v>
@@ -1600,7 +1597,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
         <x:v>63</x:v>
@@ -1626,22 +1623,22 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B28" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B28" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C28" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
         <x:v>15</x:v>
@@ -1661,7 +1658,7 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B29" s="0">
         <x:v>0</x:v>
@@ -1670,10 +1667,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>14</x:v>
@@ -1696,7 +1693,7 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B30" s="0">
         <x:v>0</x:v>
@@ -1708,7 +1705,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
         <x:v>14</x:v>
@@ -1731,7 +1728,7 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B31" s="0">
         <x:v>0</x:v>
@@ -1743,7 +1740,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
         <x:v>14</x:v>
@@ -1766,19 +1763,19 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
+      <x:c r="E32" s="0" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>14</x:v>
@@ -1810,10 +1807,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>14</x:v>
@@ -1886,7 +1883,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
         <x:v>15</x:v>
@@ -1895,13 +1892,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
@@ -1985,10 +1982,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>14</x:v>
@@ -2011,7 +2008,7 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B39" s="0">
         <x:v>0</x:v>
@@ -2020,13 +2017,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
         <x:v>15</x:v>
@@ -2035,33 +2032,33 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B40" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C40" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E40" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
         <x:v>15</x:v>
@@ -2079,61 +2076,43 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:11">
-      <x:c r="A41" s="0" t="s">
+    <x:row r="42" spans="1:11">
+      <x:c r="A42" s="0" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="B41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G41" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H41" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K41" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>88</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
@@ -2141,10 +2120,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>12</x:v>
@@ -2155,19 +2134,19 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
@@ -2175,10 +2154,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>17</x:v>
@@ -2192,13 +2171,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
         <x:v>18</x:v>
@@ -2209,16 +2188,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
@@ -2226,16 +2205,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
@@ -2243,67 +2222,67 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D52" s="0" t="s">
+      <x:c r="E52" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="E52" s="0" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
+      <x:c r="E53" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="E53" s="0" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
@@ -2311,67 +2290,67 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E57" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D57" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E57" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E58" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D58" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E58" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
@@ -2379,16 +2358,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
@@ -2396,101 +2375,101 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
@@ -2498,33 +2477,33 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
@@ -2532,67 +2511,67 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D70" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
@@ -2600,50 +2579,50 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D73" s="0" t="s">
+      <x:c r="E73" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="E73" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C74" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D74" s="0" t="s">
+      <x:c r="E74" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="E74" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
@@ -2651,50 +2630,50 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C76" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C77" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
@@ -2702,33 +2681,33 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
@@ -2736,135 +2715,135 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C80" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C82" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D82" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D83" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E83" s="0" t="s">
-        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C84" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E84" s="0" t="s">
-        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
@@ -2872,16 +2851,16 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="C88" s="0" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
@@ -2889,16 +2868,16 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
@@ -2906,7 +2885,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>5</x:v>
@@ -2915,92 +2894,92 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
@@ -3008,186 +2987,186 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D98" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C104" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D104" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B104" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C104" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D104" s="0" t="s">
+      <x:c r="E104" s="0" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="E104" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B105" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C105" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D105" s="0" t="s">
+      <x:c r="E105" s="0" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="E105" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E106" s="0" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="E106" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
@@ -3195,10 +3174,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>56</x:v>
@@ -3212,10 +3191,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>56</x:v>
@@ -3226,19 +3205,19 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
@@ -3246,10 +3225,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="C110" s="0" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>59</x:v>
@@ -3260,19 +3239,19 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
@@ -3280,10 +3259,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>62</x:v>
@@ -3297,13 +3276,13 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
         <x:v>63</x:v>
@@ -3314,13 +3293,13 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C114" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C114" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
         <x:v>63</x:v>
@@ -3331,13 +3310,13 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C115" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
         <x:v>63</x:v>
@@ -3345,70 +3324,70 @@
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C116" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D116" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C117" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D117" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C118" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D118" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
@@ -3416,33 +3395,33 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="C121" s="0" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
@@ -3450,33 +3429,33 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
@@ -3484,50 +3463,50 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B125" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C125" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D125" s="0" t="s">
+      <x:c r="E125" s="0" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="E125" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C126" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D126" s="0" t="s">
+      <x:c r="E126" s="0" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="E126" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
@@ -3535,33 +3514,33 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D127" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="E127" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C128" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
@@ -3569,10 +3548,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="C129" s="0" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>76</x:v>
@@ -3583,13 +3562,13 @@
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>76</x:v>
@@ -3603,10 +3582,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>76</x:v>
@@ -3620,10 +3599,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>76</x:v>
@@ -3634,64 +3613,64 @@
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>80</x:v>
@@ -3702,13 +3681,13 @@
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>80</x:v>
@@ -3722,10 +3701,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>80</x:v>
@@ -3739,10 +3718,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>80</x:v>
@@ -3756,10 +3735,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
         <x:v>80</x:v>
@@ -3770,121 +3749,121 @@
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
@@ -3892,84 +3871,50 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E149" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C149" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D149" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E149" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="151" spans="1:11">
-      <x:c r="A151" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B151" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C151" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D151" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E151" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="152" spans="1:11">
-      <x:c r="A152" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B152" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C152" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D152" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E152" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,280 +49,277 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.03.2026</x:t>
+    <x:t>YAPRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Detaylı Kısıtlamalar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açıklama</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKISY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kredili İşlem Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açığa Satış Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBRUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>16.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YIGIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Detaylı Kısıtlamalar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açıklama</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKISY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PBRUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.04.2026</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -731,19 +728,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -760,60 +757,60 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="E4" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
@@ -827,63 +824,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -897,19 +894,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>14</x:v>
@@ -923,7 +920,7 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="0">
         <x:v>0</x:v>
@@ -932,19 +929,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
         <x:v>15</x:v>
@@ -958,7 +955,7 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -967,33 +964,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="0">
         <x:v>0</x:v>
@@ -1002,33 +999,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="0">
         <x:v>0</x:v>
@@ -1037,63 +1034,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
+      <x:c r="E12" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
@@ -1107,33 +1104,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B14" s="0">
         <x:v>0</x:v>
@@ -1142,33 +1139,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B15" s="0">
         <x:v>0</x:v>
@@ -1177,33 +1174,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="0">
         <x:v>0</x:v>
@@ -1212,54 +1209,54 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B17" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B17" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
         <x:v>14</x:v>
@@ -1285,30 +1282,30 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1317,19 +1314,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
         <x:v>15</x:v>
@@ -1343,7 +1340,7 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B20" s="0">
         <x:v>0</x:v>
@@ -1352,33 +1349,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B21" s="0">
         <x:v>0</x:v>
@@ -1387,19 +1384,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
         <x:v>14</x:v>
@@ -1413,28 +1410,28 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
+      <x:c r="E22" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
         <x:v>15</x:v>
@@ -1466,19 +1463,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -1498,22 +1495,22 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -1536,19 +1533,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -1565,30 +1562,30 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B27" s="0">
         <x:v>0</x:v>
@@ -1597,33 +1594,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B28" s="0">
         <x:v>0</x:v>
@@ -1632,33 +1629,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B29" s="0">
         <x:v>0</x:v>
@@ -1667,33 +1664,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B30" s="0">
         <x:v>0</x:v>
@@ -1702,33 +1699,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B31" s="0">
         <x:v>0</x:v>
@@ -1740,25 +1737,25 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
@@ -1769,66 +1766,66 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.1512</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
@@ -1842,19 +1839,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
         <x:v>14</x:v>
@@ -1868,28 +1865,28 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
         <x:v>15</x:v>
@@ -1912,19 +1909,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
         <x:v>14</x:v>
@@ -1938,7 +1935,7 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B37" s="0">
         <x:v>0</x:v>
@@ -1947,19 +1944,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
         <x:v>15</x:v>
@@ -1973,7 +1970,7 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B38" s="0">
         <x:v>0</x:v>
@@ -1982,33 +1979,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B39" s="0">
         <x:v>0</x:v>
@@ -2017,33 +2014,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B40" s="0">
         <x:v>0</x:v>
@@ -2052,33 +2049,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
@@ -2086,10 +2083,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>3</x:v>
@@ -2103,10 +2100,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>12</x:v>
@@ -2120,10 +2117,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>12</x:v>
@@ -2134,19 +2131,19 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
@@ -2163,7 +2160,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
@@ -2171,67 +2168,67 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
+      <x:c r="E50" s="0" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="E50" s="0" t="s">
-        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D51" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
@@ -2239,16 +2236,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
@@ -2256,50 +2253,50 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E54" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D55" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E55" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
@@ -2307,16 +2304,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
@@ -2324,89 +2321,89 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>90</x:v>
@@ -2415,66 +2412,66 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>90</x:v>
@@ -2483,32 +2480,32 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>90</x:v>
@@ -2517,32 +2514,32 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>90</x:v>
@@ -2551,27 +2548,27 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E70" s="0" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="E70" s="0" t="s">
-        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
+      <x:c r="E71" s="0" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="E71" s="0" t="s">
-        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
@@ -2585,10 +2582,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
@@ -2596,38 +2593,38 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>90</x:v>
@@ -2636,15 +2633,15 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>90</x:v>
@@ -2653,49 +2650,49 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>90</x:v>
@@ -2704,112 +2701,112 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C80" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E80" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C81" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D81" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E81" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
@@ -2826,7 +2823,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
@@ -2834,305 +2831,305 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B102" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D102" s="0" t="s">
+      <x:c r="E102" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E102" s="0" t="s">
-        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B103" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C103" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D103" s="0" t="s">
+      <x:c r="E103" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E103" s="0" t="s">
-        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
@@ -3140,10 +3137,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>53</x:v>
@@ -3157,13 +3154,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
         <x:v>54</x:v>
@@ -3174,10 +3171,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>56</x:v>
@@ -3191,10 +3188,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>56</x:v>
@@ -3225,10 +3222,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>59</x:v>
@@ -3239,19 +3236,19 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
@@ -3259,16 +3256,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
@@ -3276,21 +3273,21 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>90</x:v>
@@ -3299,66 +3296,66 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>90</x:v>
@@ -3367,95 +3364,95 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
@@ -3463,16 +3460,16 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
@@ -3486,15 +3483,15 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>90</x:v>
@@ -3503,27 +3500,27 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D127" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E127" s="0" t="s">
-        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
@@ -3531,16 +3528,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
@@ -3548,38 +3545,38 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>98</x:v>
@@ -3588,78 +3585,78 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E134" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C134" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D134" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E134" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E135" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C135" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D135" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E135" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
@@ -3667,16 +3664,16 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
@@ -3684,38 +3681,38 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>96</x:v>
@@ -3724,15 +3721,15 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>90</x:v>
@@ -3741,151 +3738,151 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>90</x:v>
@@ -3894,27 +3891,27 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,226 +49,229 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>YAPRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.02.2026</x:t>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
   </x:si>
   <x:si>
     <x:t>17.04.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>ANELE</x:t>
   </x:si>
   <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YIGIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
   </x:si>
   <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
@@ -280,40 +283,37 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PASKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açığa Satış Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PKISY</x:t>
   </x:si>
   <x:si>
     <x:t>Kredili İşlem Yasağı</x:t>
   </x:si>
   <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
   <x:si>
     <x:t>PBRUT</x:t>
   </x:si>
   <x:si>
-    <x:t>18.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
     <x:t>PYAYN</x:t>
   </x:si>
   <x:si>
     <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
   <x:si>
     <x:t>06.04.2026</x:t>
@@ -670,7 +670,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K150"/>
+  <x:dimension ref="A1:K152"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -728,19 +728,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -754,7 +754,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>13</x:v>
@@ -763,59 +763,59 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>37.9</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>1.23</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="E4" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>0</x:v>
@@ -824,19 +824,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>15</x:v>
@@ -850,42 +850,42 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0">
         <x:v>0</x:v>
@@ -894,19 +894,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>14</x:v>
@@ -920,7 +920,7 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="0">
         <x:v>0</x:v>
@@ -929,33 +929,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -964,63 +964,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
@@ -1034,68 +1034,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="0">
         <x:v>0</x:v>
@@ -1104,33 +1104,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B14" s="0">
         <x:v>0</x:v>
@@ -1139,33 +1139,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B15" s="0">
         <x:v>0</x:v>
@@ -1174,19 +1174,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
         <x:v>15</x:v>
@@ -1200,28 +1200,28 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B16" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B16" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
+      <x:c r="E16" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>15</x:v>
@@ -1244,19 +1244,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
         <x:v>14</x:v>
@@ -1270,7 +1270,7 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B18" s="0">
         <x:v>0</x:v>
@@ -1279,19 +1279,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
         <x:v>14</x:v>
@@ -1305,7 +1305,7 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1314,19 +1314,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
         <x:v>15</x:v>
@@ -1340,37 +1340,37 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
@@ -1387,16 +1387,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
         <x:v>14</x:v>
@@ -1410,7 +1410,7 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B22" s="0">
         <x:v>0</x:v>
@@ -1419,33 +1419,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B23" s="0">
         <x:v>0</x:v>
@@ -1454,63 +1454,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -1524,33 +1524,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B26" s="0">
         <x:v>0</x:v>
@@ -1559,33 +1559,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B27" s="0">
         <x:v>0</x:v>
@@ -1594,63 +1594,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B28" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B28" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C28" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
@@ -1664,89 +1664,89 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="F31" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
         <x:v>15</x:v>
@@ -1760,63 +1760,63 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>-0.1512</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
         <x:v>15</x:v>
@@ -1830,7 +1830,7 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B34" s="0">
         <x:v>0</x:v>
@@ -1839,19 +1839,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
         <x:v>14</x:v>
@@ -1865,7 +1865,7 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B35" s="0">
         <x:v>0</x:v>
@@ -1874,33 +1874,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B36" s="0">
         <x:v>0</x:v>
@@ -1909,19 +1909,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
         <x:v>14</x:v>
@@ -1935,7 +1935,7 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B37" s="0">
         <x:v>0</x:v>
@@ -1944,63 +1944,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B38" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B38" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C38" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
@@ -2014,28 +2014,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
@@ -2049,67 +2049,85 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:11">
+      <x:c r="A41" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="F40" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G40" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H40" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I40" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J40" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K40" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:11">
-      <x:c r="A42" s="0" t="s">
-        <x:v>85</x:v>
+      <x:c r="E41" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K41" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
@@ -2117,10 +2135,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>12</x:v>
@@ -2134,13 +2152,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
         <x:v>13</x:v>
@@ -2151,13 +2169,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
         <x:v>13</x:v>
@@ -2168,13 +2186,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
         <x:v>13</x:v>
@@ -2182,325 +2200,325 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
+      <x:c r="E50" s="0" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="E50" s="0" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D51" s="0" t="s">
+      <x:c r="E51" s="0" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="E51" s="0" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="E52" s="0" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="E53" s="0" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D63" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D65" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D66" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E66" s="0" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E67" s="0" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D67" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E67" s="0" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
@@ -2508,543 +2526,543 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D70" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C75" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D75" s="0" t="s">
+      <x:c r="E75" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="E75" s="0" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E76" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="E76" s="0" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E77" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="E77" s="0" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E78" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="E78" s="0" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="E79" s="0" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B91" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C91" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D91" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
@@ -3052,16 +3070,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
@@ -3069,135 +3087,135 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C104" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C104" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E107" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="B107" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D107" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E107" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E108" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="B108" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D108" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E108" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
@@ -3205,16 +3223,16 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C109" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
@@ -3222,50 +3240,50 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
@@ -3273,84 +3291,84 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C113" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C115" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D115" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E116" s="0" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C116" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D116" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E116" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E117" s="0" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C117" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D117" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E117" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
@@ -3358,492 +3376,492 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C118" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C120" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D120" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C121" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D121" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E122" s="0" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="B122" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C122" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D122" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E122" s="0" t="s">
-        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E123" s="0" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="B123" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C123" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D123" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E123" s="0" t="s">
-        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D127" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E127" s="0" t="s">
-        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C130" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C133" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E139" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="E139" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C140" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D140" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E140" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="E140" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="E141" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="E141" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C142" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D142" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E142" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="E142" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E143" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="E143" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D144" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E144" s="0" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="B144" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C144" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D144" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E144" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E145" s="0" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="B145" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C145" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D145" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E145" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
@@ -3851,16 +3869,16 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
@@ -3868,16 +3886,16 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C148" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
@@ -3885,16 +3903,16 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C149" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
@@ -3902,16 +3920,50 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E150" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:11">
+      <x:c r="A151" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D151" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E151" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:11">
+      <x:c r="A152" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="D150" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E150" s="0" t="s">
+      <x:c r="C152" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D152" s="0" t="s">
         <x:v>83</x:v>
+      </x:c>
+      <x:c r="E152" s="0" t="s">
+        <x:v>81</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -272,6 +272,21 @@
   </x:si>
   <x:si>
     <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
   </x:si>
   <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
@@ -670,7 +685,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K152"/>
+  <x:dimension ref="A1:K166"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -783,10 +798,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>37.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>1.23</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>18</x:v>
@@ -1171,7 +1186,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.9138</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>36</x:v>
@@ -2108,88 +2123,142 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
+    <x:row r="42" spans="1:11">
+      <x:c r="A42" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B42" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C42" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J42" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K42" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B43" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C43" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J43" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K43" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B44" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C44" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C44" s="0" t="s">
+      <x:c r="E44" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:11">
-      <x:c r="A45" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E45" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="F44" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J44" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K44" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>12</x:v>
@@ -2200,64 +2269,64 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>18</x:v>
@@ -2268,13 +2337,13 @@
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>18</x:v>
@@ -2288,10 +2357,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>18</x:v>
@@ -2305,10 +2374,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>18</x:v>
@@ -2322,10 +2391,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>18</x:v>
@@ -2336,16 +2405,16 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
         <x:v>19</x:v>
@@ -2353,16 +2422,16 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
         <x:v>19</x:v>
@@ -2370,16 +2439,16 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
         <x:v>19</x:v>
@@ -2387,13 +2456,13 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>22</x:v>
@@ -2404,13 +2473,13 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>22</x:v>
@@ -2421,13 +2490,13 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>22</x:v>
@@ -2438,16 +2507,16 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
         <x:v>19</x:v>
@@ -2455,16 +2524,16 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
         <x:v>19</x:v>
@@ -2472,64 +2541,64 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>28</x:v>
@@ -2540,16 +2609,16 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
         <x:v>29</x:v>
@@ -2557,16 +2626,16 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
         <x:v>29</x:v>
@@ -2574,16 +2643,16 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
         <x:v>29</x:v>
@@ -2591,13 +2660,13 @@
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>32</x:v>
@@ -2608,13 +2677,13 @@
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>32</x:v>
@@ -2625,13 +2694,13 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>32</x:v>
@@ -2642,53 +2711,53 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
@@ -2696,10 +2765,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>36</x:v>
@@ -2713,10 +2782,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>36</x:v>
@@ -2730,10 +2799,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>36</x:v>
@@ -2744,16 +2813,16 @@
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
         <x:v>37</x:v>
@@ -2761,16 +2830,16 @@
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
         <x:v>37</x:v>
@@ -2778,16 +2847,16 @@
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
         <x:v>37</x:v>
@@ -2798,10 +2867,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>39</x:v>
@@ -2815,10 +2884,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>39</x:v>
@@ -2832,10 +2901,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>39</x:v>
@@ -2846,13 +2915,13 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>39</x:v>
@@ -2863,13 +2932,13 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>39</x:v>
@@ -2880,13 +2949,13 @@
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>39</x:v>
@@ -2897,13 +2966,13 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>39</x:v>
@@ -2914,16 +2983,16 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C91" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
         <x:v>37</x:v>
@@ -2931,16 +3000,16 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
         <x:v>37</x:v>
@@ -2948,16 +3017,16 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
         <x:v>37</x:v>
@@ -2968,10 +3037,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>43</x:v>
@@ -2985,10 +3054,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>43</x:v>
@@ -3002,10 +3071,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>43</x:v>
@@ -3016,186 +3085,186 @@
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C99" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C106" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
         <x:v>55</x:v>
@@ -3203,16 +3272,16 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
         <x:v>55</x:v>
@@ -3220,13 +3289,13 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>57</x:v>
@@ -3237,13 +3306,13 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>57</x:v>
@@ -3254,16 +3323,16 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
         <x:v>55</x:v>
@@ -3271,16 +3340,16 @@
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
         <x:v>55</x:v>
@@ -3288,16 +3357,16 @@
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
         <x:v>55</x:v>
@@ -3305,13 +3374,13 @@
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>60</x:v>
@@ -3322,64 +3391,64 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>63</x:v>
@@ -3390,64 +3459,64 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>67</x:v>
@@ -3458,13 +3527,13 @@
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>67</x:v>
@@ -3478,10 +3547,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>67</x:v>
@@ -3512,10 +3581,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
         <x:v>67</x:v>
@@ -3526,64 +3595,64 @@
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>71</x:v>
@@ -3594,13 +3663,13 @@
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>71</x:v>
@@ -3614,10 +3683,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>71</x:v>
@@ -3631,10 +3700,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
         <x:v>71</x:v>
@@ -3648,10 +3717,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>71</x:v>
@@ -3662,13 +3731,13 @@
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
         <x:v>71</x:v>
@@ -3679,13 +3748,13 @@
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>71</x:v>
@@ -3696,13 +3765,13 @@
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>71</x:v>
@@ -3713,13 +3782,13 @@
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>71</x:v>
@@ -3730,67 +3799,67 @@
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
         <x:v>77</x:v>
@@ -3798,16 +3867,16 @@
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
         <x:v>77</x:v>
@@ -3815,67 +3884,67 @@
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C146" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
         <x:v>81</x:v>
@@ -3883,16 +3952,16 @@
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
         <x:v>81</x:v>
@@ -3900,13 +3969,13 @@
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
         <x:v>83</x:v>
@@ -3917,13 +3986,13 @@
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>83</x:v>
@@ -3934,13 +4003,13 @@
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>83</x:v>
@@ -3951,19 +4020,257 @@
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
         <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:11">
+      <x:c r="A153" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E153" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:11">
+      <x:c r="A154" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D154" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E154" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:11">
+      <x:c r="A155" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D155" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E155" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:11">
+      <x:c r="A156" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D156" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E156" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:11">
+      <x:c r="A157" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E157" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:11">
+      <x:c r="A158" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E158" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:11">
+      <x:c r="A159" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E159" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:11">
+      <x:c r="A160" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D160" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E160" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:11">
+      <x:c r="A161" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E161" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:11">
+      <x:c r="A162" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E162" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:11">
+      <x:c r="A163" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D163" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E163" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:11">
+      <x:c r="A164" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D164" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E164" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:11">
+      <x:c r="A165" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D165" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E165" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:11">
+      <x:c r="A166" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D166" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E166" s="0" t="s">
+        <x:v>88</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -287,6 +287,15 @@
   </x:si>
   <x:si>
     <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
   </x:si>
   <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
@@ -685,7 +694,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K166"/>
+  <x:dimension ref="A1:K173"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1186,7 +1195,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>-0.9138</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>36</x:v>
@@ -2228,71 +2237,107 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
+    <x:row r="45" spans="1:11">
+      <x:c r="A45" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B45" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C45" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J45" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K45" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:11">
-      <x:c r="A47" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B46" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C46" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
-        <x:v>4</x:v>
+      <x:c r="F46" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J46" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K46" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>12</x:v>
@@ -2303,13 +2348,13 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>12</x:v>
@@ -2320,47 +2365,47 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>18</x:v>
@@ -2371,13 +2416,13 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>18</x:v>
@@ -2391,10 +2436,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>18</x:v>
@@ -2408,10 +2453,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>18</x:v>
@@ -2425,10 +2470,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>18</x:v>
@@ -2442,10 +2487,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>18</x:v>
@@ -2456,16 +2501,16 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
         <x:v>19</x:v>
@@ -2473,16 +2518,16 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
         <x:v>19</x:v>
@@ -2490,13 +2535,13 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>22</x:v>
@@ -2507,13 +2552,13 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>22</x:v>
@@ -2524,13 +2569,13 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>22</x:v>
@@ -2541,13 +2586,13 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>22</x:v>
@@ -2558,16 +2603,16 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
         <x:v>19</x:v>
@@ -2575,16 +2620,16 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
         <x:v>19</x:v>
@@ -2592,47 +2637,47 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>28</x:v>
@@ -2643,13 +2688,13 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>28</x:v>
@@ -2660,16 +2705,16 @@
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
         <x:v>29</x:v>
@@ -2677,16 +2722,16 @@
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
         <x:v>29</x:v>
@@ -2694,13 +2739,13 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>32</x:v>
@@ -2711,13 +2756,13 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>32</x:v>
@@ -2728,13 +2773,13 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>32</x:v>
@@ -2745,13 +2790,13 @@
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>32</x:v>
@@ -2762,36 +2807,36 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C78" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C79" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
@@ -2799,10 +2844,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>36</x:v>
@@ -2816,10 +2861,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>36</x:v>
@@ -2833,10 +2878,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>36</x:v>
@@ -2850,10 +2895,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>36</x:v>
@@ -2864,16 +2909,16 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
         <x:v>37</x:v>
@@ -2881,16 +2926,16 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
         <x:v>37</x:v>
@@ -2901,10 +2946,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="C86" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>39</x:v>
@@ -2935,10 +2980,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>39</x:v>
@@ -2952,10 +2997,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>39</x:v>
@@ -2966,13 +3011,13 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>39</x:v>
@@ -2983,13 +3028,13 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>39</x:v>
@@ -3000,13 +3045,13 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>39</x:v>
@@ -3017,13 +3062,13 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>39</x:v>
@@ -3034,16 +3079,16 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
         <x:v>37</x:v>
@@ -3051,16 +3096,16 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
         <x:v>37</x:v>
@@ -3071,10 +3116,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>43</x:v>
@@ -3088,10 +3133,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>43</x:v>
@@ -3105,10 +3150,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>43</x:v>
@@ -3122,10 +3167,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>43</x:v>
@@ -3136,36 +3181,36 @@
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
@@ -3173,13 +3218,13 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
         <x:v>46</x:v>
@@ -3187,104 +3232,104 @@
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
@@ -3292,13 +3337,13 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
         <x:v>55</x:v>
@@ -3306,16 +3351,16 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
         <x:v>55</x:v>
@@ -3323,13 +3368,13 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>57</x:v>
@@ -3340,13 +3385,13 @@
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>57</x:v>
@@ -3357,13 +3402,13 @@
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>57</x:v>
@@ -3374,16 +3419,16 @@
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
         <x:v>55</x:v>
@@ -3391,16 +3436,16 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
         <x:v>55</x:v>
@@ -3408,13 +3453,13 @@
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>60</x:v>
@@ -3425,13 +3470,13 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>60</x:v>
@@ -3442,47 +3487,47 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>63</x:v>
@@ -3493,13 +3538,13 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>63</x:v>
@@ -3510,47 +3555,47 @@
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="C124" s="0" t="s">
-        <x:v>101</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>67</x:v>
@@ -3561,13 +3606,13 @@
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="C125" s="0" t="s">
-        <x:v>99</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>67</x:v>
@@ -3581,10 +3626,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
         <x:v>67</x:v>
@@ -3598,10 +3643,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>67</x:v>
@@ -3615,10 +3660,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>67</x:v>
@@ -3632,10 +3677,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>67</x:v>
@@ -3646,47 +3691,47 @@
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="C132" s="0" t="s">
-        <x:v>101</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>71</x:v>
@@ -3697,13 +3742,13 @@
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
         <x:v>71</x:v>
@@ -3717,10 +3762,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>71</x:v>
@@ -3734,10 +3779,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
         <x:v>71</x:v>
@@ -3751,10 +3796,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>71</x:v>
@@ -3768,10 +3813,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>71</x:v>
@@ -3782,13 +3827,13 @@
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>71</x:v>
@@ -3799,13 +3844,13 @@
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>71</x:v>
@@ -3816,13 +3861,13 @@
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
         <x:v>71</x:v>
@@ -3833,13 +3878,13 @@
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
         <x:v>71</x:v>
@@ -3850,36 +3895,36 @@
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
@@ -3887,13 +3932,13 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
         <x:v>77</x:v>
@@ -3901,16 +3946,16 @@
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
         <x:v>77</x:v>
@@ -3918,16 +3963,16 @@
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
         <x:v>77</x:v>
@@ -3935,36 +3980,36 @@
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
@@ -3972,13 +4017,13 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
         <x:v>81</x:v>
@@ -3986,16 +4031,16 @@
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
         <x:v>81</x:v>
@@ -4003,13 +4048,13 @@
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>83</x:v>
@@ -4020,13 +4065,13 @@
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
         <x:v>83</x:v>
@@ -4037,13 +4082,13 @@
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>83</x:v>
@@ -4054,13 +4099,13 @@
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>83</x:v>
@@ -4071,13 +4116,13 @@
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>83</x:v>
@@ -4088,36 +4133,36 @@
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C157" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
@@ -4125,10 +4170,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
         <x:v>87</x:v>
@@ -4139,13 +4184,13 @@
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>87</x:v>
@@ -4156,13 +4201,13 @@
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
         <x:v>87</x:v>
@@ -4193,10 +4238,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
         <x:v>87</x:v>
@@ -4210,10 +4255,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>87</x:v>
@@ -4227,10 +4272,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>87</x:v>
@@ -4241,13 +4286,13 @@
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>87</x:v>
@@ -4258,19 +4303,138 @@
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
       <x:c r="E166" s="0" t="s">
         <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:11">
+      <x:c r="A167" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E167" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:11">
+      <x:c r="A168" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E168" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:11">
+      <x:c r="A169" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E169" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:11">
+      <x:c r="A170" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E170" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:11">
+      <x:c r="A171" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E171" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:11">
+      <x:c r="A172" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E172" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:11">
+      <x:c r="A173" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E173" s="0" t="s">
+        <x:v>92</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,255 +49,252 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.03.2026</x:t>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
     <x:t>22.04.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YIGIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
     <x:t>21.05.2026</x:t>
   </x:si>
   <x:si>
     <x:t>KONTR</x:t>
   </x:si>
   <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
   </x:si>
   <x:si>
@@ -319,25 +316,25 @@
     <x:t>Kredili İşlem Yasağı</x:t>
   </x:si>
   <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBRUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
     <x:t>PEIAK</x:t>
   </x:si>
   <x:si>
     <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PBRUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
   </x:si>
   <x:si>
     <x:t>06.04.2026</x:t>
@@ -694,7 +691,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K173"/>
+  <x:dimension ref="A1:K170"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -784,7 +781,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>15</x:v>
@@ -793,13 +790,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
@@ -816,7 +813,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>14</x:v>
@@ -839,7 +836,7 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>0</x:v>
@@ -851,10 +848,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>15</x:v>
@@ -863,18 +860,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -883,10 +880,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>14</x:v>
@@ -909,7 +906,7 @@
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="0">
         <x:v>0</x:v>
@@ -921,7 +918,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>14</x:v>
@@ -944,19 +941,19 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>14</x:v>
@@ -979,19 +976,19 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="B9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>14</x:v>
@@ -1026,7 +1023,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>14</x:v>
@@ -1049,7 +1046,7 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B11" s="0">
         <x:v>0</x:v>
@@ -1061,7 +1058,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>14</x:v>
@@ -1084,7 +1081,7 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B12" s="0">
         <x:v>0</x:v>
@@ -1093,10 +1090,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>14</x:v>
@@ -1119,7 +1116,7 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B13" s="0">
         <x:v>0</x:v>
@@ -1131,10 +1128,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>15</x:v>
@@ -1143,13 +1140,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
@@ -1163,13 +1160,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>15</x:v>
@@ -1178,33 +1175,33 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
         <x:v>15</x:v>
@@ -1213,18 +1210,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B16" s="0">
         <x:v>0</x:v>
@@ -1233,13 +1230,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
         <x:v>15</x:v>
@@ -1248,18 +1245,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1271,10 +1268,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
         <x:v>15</x:v>
@@ -1283,33 +1280,33 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>15</x:v>
@@ -1329,7 +1326,7 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1338,13 +1335,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
         <x:v>15</x:v>
@@ -1353,18 +1350,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B20" s="0">
         <x:v>0</x:v>
@@ -1373,13 +1370,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
         <x:v>15</x:v>
@@ -1399,7 +1396,7 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B21" s="0">
         <x:v>0</x:v>
@@ -1408,13 +1405,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
         <x:v>15</x:v>
@@ -1434,7 +1431,7 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B22" s="0">
         <x:v>0</x:v>
@@ -1443,10 +1440,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>14</x:v>
@@ -1469,22 +1466,22 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
         <x:v>15</x:v>
@@ -1504,19 +1501,19 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>14</x:v>
@@ -1539,7 +1536,7 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B25" s="0">
         <x:v>0</x:v>
@@ -1548,10 +1545,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>14</x:v>
@@ -1574,19 +1571,19 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
+      <x:c r="E26" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>14</x:v>
@@ -1618,10 +1615,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>14</x:v>
@@ -1694,7 +1691,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
         <x:v>15</x:v>
@@ -1703,13 +1700,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
@@ -1793,10 +1790,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>14</x:v>
@@ -1819,7 +1816,7 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B33" s="0">
         <x:v>0</x:v>
@@ -1828,13 +1825,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
         <x:v>15</x:v>
@@ -1843,18 +1840,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B34" s="0">
         <x:v>0</x:v>
@@ -1863,13 +1860,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
         <x:v>15</x:v>
@@ -1889,19 +1886,19 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>14</x:v>
@@ -1933,7 +1930,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
         <x:v>77</x:v>
@@ -2003,13 +2000,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
         <x:v>15</x:v>
@@ -2029,7 +2026,7 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B39" s="0">
         <x:v>0</x:v>
@@ -2038,10 +2035,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
         <x:v>14</x:v>
@@ -2064,7 +2061,7 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B40" s="0">
         <x:v>0</x:v>
@@ -2076,7 +2073,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
         <x:v>14</x:v>
@@ -2091,7 +2088,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
         <x:v>14</x:v>
@@ -2111,10 +2108,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
         <x:v>15</x:v>
@@ -2123,13 +2120,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
@@ -2143,10 +2140,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
         <x:v>14</x:v>
@@ -2161,7 +2158,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J42" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
         <x:v>14</x:v>
@@ -2169,22 +2166,22 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B43" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C43" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B43" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C43" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
         <x:v>15</x:v>
@@ -2193,13 +2190,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I43" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J43" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -2213,10 +2210,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
         <x:v>14</x:v>
@@ -2266,67 +2263,49 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J45" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" spans="1:11">
-      <x:c r="A46" s="0" t="s">
+    <x:row r="47" spans="1:11">
+      <x:c r="A47" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="B46" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C46" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="F46" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G46" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H46" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I46" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J46" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K46" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>94</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
@@ -2334,10 +2313,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>12</x:v>
@@ -2348,13 +2327,13 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>12</x:v>
@@ -2368,10 +2347,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>12</x:v>
@@ -2385,10 +2364,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>12</x:v>
@@ -2399,121 +2378,121 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
@@ -2521,33 +2500,33 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
@@ -2555,33 +2534,33 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
@@ -2589,84 +2568,84 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D66" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D67" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E68" s="0" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D68" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E68" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E69" s="0" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D69" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E69" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
@@ -2674,50 +2653,50 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
@@ -2725,33 +2704,33 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
@@ -2759,271 +2738,271 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C81" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D81" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C82" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D82" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D83" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C84" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C85" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D85" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
@@ -3031,407 +3010,407 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="C94" s="0" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="C95" s="0" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E97" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D97" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E97" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E98" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D98" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E98" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E99" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B99" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C99" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D99" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E99" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C103" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C105" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="D107" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E107" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E107" s="0" t="s">
-        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="D108" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E108" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E108" s="0" t="s">
-        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B109" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C109" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D109" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B110" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C110" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D110" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C112" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D112" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C113" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D113" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
@@ -3439,50 +3418,50 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C116" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D116" s="0" t="s">
+      <x:c r="E116" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="E116" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C117" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D117" s="0" t="s">
+      <x:c r="E117" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="E117" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
@@ -3490,33 +3469,33 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C118" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="D118" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E118" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="E118" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C119" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
@@ -3524,10 +3503,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="C120" s="0" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>63</x:v>
@@ -3538,13 +3517,13 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>63</x:v>
@@ -3558,10 +3537,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>63</x:v>
@@ -3575,10 +3554,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>63</x:v>
@@ -3589,64 +3568,64 @@
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C126" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>67</x:v>
@@ -3657,13 +3636,13 @@
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>67</x:v>
@@ -3677,10 +3656,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>67</x:v>
@@ -3694,10 +3673,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>67</x:v>
@@ -3711,10 +3690,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>67</x:v>
@@ -3725,41 +3704,41 @@
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>103</x:v>
@@ -3768,163 +3747,163 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E139" s="0" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="B139" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C139" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D139" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E139" s="0" t="s">
-        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D142" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C142" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D142" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D143" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B143" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C143" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D143" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
@@ -3932,13 +3911,13 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C144" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
         <x:v>77</x:v>
@@ -3949,13 +3928,13 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C145" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
         <x:v>77</x:v>
@@ -3966,13 +3945,13 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
         <x:v>77</x:v>
@@ -3983,10 +3962,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="C147" s="0" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
         <x:v>79</x:v>
@@ -4000,10 +3979,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="C148" s="0" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>79</x:v>
@@ -4017,16 +3996,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
@@ -4034,50 +4013,50 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C152" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
@@ -4085,50 +4064,50 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="C153" s="0" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
@@ -4136,16 +4115,16 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
@@ -4153,169 +4132,169 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C159" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C160" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E161" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D164" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E164" s="0" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="B164" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C164" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D164" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="E164" s="0" t="s">
-        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D165" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E165" s="0" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="B165" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C165" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D165" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="E165" s="0" t="s">
-        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E166" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
@@ -4323,16 +4302,16 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C167" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E167" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
@@ -4340,16 +4319,16 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C168" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E168" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
@@ -4357,10 +4336,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="C169" s="0" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
         <x:v>13</x:v>
@@ -4374,66 +4353,15 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="C170" s="0" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E170" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" spans="1:11">
-      <x:c r="A171" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B171" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C171" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D171" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E171" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" spans="1:11">
-      <x:c r="A172" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B172" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C172" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D172" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E172" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" spans="1:11">
-      <x:c r="A173" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B173" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C173" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D173" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E173" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,250 +49,247 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>ECOGR</x:t>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
   </x:si>
   <x:si>
     <x:t>25.03.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YIGIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
+    <x:t>26.05.2026</x:t>
   </x:si>
   <x:si>
     <x:t>DGNMO</x:t>
   </x:si>
   <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
@@ -325,22 +322,28 @@
     <x:t>PBRUT</x:t>
   </x:si>
   <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PPEGK</x:t>
   </x:si>
   <x:si>
     <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
   <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
     <x:t>06.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>16.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PTEKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
   </x:si>
 </x:sst>
 </file>
@@ -691,7 +694,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K170"/>
+  <x:dimension ref="A1:K166"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -781,7 +784,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>15</x:v>
@@ -790,13 +793,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
@@ -918,10 +921,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>15</x:v>
@@ -930,33 +933,33 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
         <x:v>15</x:v>
@@ -965,13 +968,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
@@ -985,10 +988,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>14</x:v>
@@ -1020,10 +1023,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>14</x:v>
@@ -1046,22 +1049,22 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>15</x:v>
@@ -1070,13 +1073,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
@@ -1090,13 +1093,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
         <x:v>15</x:v>
@@ -1116,7 +1119,7 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="0">
         <x:v>0</x:v>
@@ -1125,13 +1128,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>15</x:v>
@@ -1140,18 +1143,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B14" s="0">
         <x:v>0</x:v>
@@ -1160,13 +1163,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>15</x:v>
@@ -1175,18 +1178,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="0">
         <x:v>0</x:v>
@@ -1195,13 +1198,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
         <x:v>15</x:v>
@@ -1221,7 +1224,7 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B16" s="0">
         <x:v>0</x:v>
@@ -1230,10 +1233,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>14</x:v>
@@ -1256,7 +1259,7 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1265,13 +1268,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
         <x:v>15</x:v>
@@ -1280,18 +1283,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="0">
         <x:v>0</x:v>
@@ -1300,13 +1303,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>15</x:v>
@@ -1326,7 +1329,7 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1335,10 +1338,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>14</x:v>
@@ -1361,7 +1364,7 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="0">
         <x:v>0</x:v>
@@ -1370,10 +1373,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>14</x:v>
@@ -1396,22 +1399,22 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B21" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C21" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B21" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C21" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
+      <x:c r="E21" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
         <x:v>15</x:v>
@@ -1443,10 +1446,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
         <x:v>15</x:v>
@@ -1455,18 +1458,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B23" s="0">
         <x:v>0</x:v>
@@ -1475,10 +1478,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>14</x:v>
@@ -1501,7 +1504,7 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="0">
         <x:v>0</x:v>
@@ -1513,10 +1516,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
         <x:v>15</x:v>
@@ -1525,18 +1528,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B25" s="0">
         <x:v>0</x:v>
@@ -1548,7 +1551,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>14</x:v>
@@ -1571,7 +1574,7 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B26" s="0">
         <x:v>0</x:v>
@@ -1580,10 +1583,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>14</x:v>
@@ -1615,13 +1618,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
         <x:v>15</x:v>
@@ -1641,19 +1644,19 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B28" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="B28" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C28" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>14</x:v>
@@ -1685,10 +1688,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>15</x:v>
@@ -1700,30 +1703,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
         <x:v>14</x:v>
@@ -1755,13 +1758,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
         <x:v>15</x:v>
@@ -1770,13 +1773,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
@@ -1790,10 +1793,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>14</x:v>
@@ -1825,10 +1828,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>14</x:v>
@@ -1843,7 +1846,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
         <x:v>14</x:v>
@@ -1851,16 +1854,16 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="B34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
         <x:v>73</x:v>
@@ -1875,18 +1878,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B35" s="0">
         <x:v>0</x:v>
@@ -1895,7 +1898,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
         <x:v>73</x:v>
@@ -1930,13 +1933,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
         <x:v>15</x:v>
@@ -1948,7 +1951,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
         <x:v>14</x:v>
@@ -1956,19 +1959,19 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>14</x:v>
@@ -2000,10 +2003,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>14</x:v>
@@ -2026,7 +2029,7 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B39" s="0">
         <x:v>0</x:v>
@@ -2035,13 +2038,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
         <x:v>15</x:v>
@@ -2050,18 +2053,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B40" s="0">
         <x:v>0</x:v>
@@ -2070,13 +2073,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
         <x:v>15</x:v>
@@ -2088,7 +2091,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
         <x:v>14</x:v>
@@ -2096,22 +2099,22 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
         <x:v>15</x:v>
@@ -2120,18 +2123,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B42" s="0">
         <x:v>0</x:v>
@@ -2140,10 +2143,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
         <x:v>14</x:v>
@@ -2166,7 +2169,7 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B43" s="0">
         <x:v>0</x:v>
@@ -2175,10 +2178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
         <x:v>14</x:v>
@@ -2193,113 +2196,77 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J43" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:11">
-      <x:c r="A44" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B44" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C44" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F44" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G44" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H44" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I44" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J44" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K44" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B45" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C45" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E45" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G45" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H45" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I45" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J45" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K45" s="0" t="s">
-        <x:v>14</x:v>
+    </x:row>
+    <x:row r="46" spans="1:11">
+      <x:c r="A46" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>12</x:v>
@@ -2310,13 +2277,13 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>99</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>12</x:v>
@@ -2327,16 +2294,16 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>13</x:v>
@@ -2344,16 +2311,16 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
         <x:v>13</x:v>
@@ -2361,16 +2328,16 @@
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
         <x:v>13</x:v>
@@ -2378,16 +2345,16 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
         <x:v>13</x:v>
@@ -2395,16 +2362,16 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
         <x:v>13</x:v>
@@ -2412,16 +2379,16 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
         <x:v>13</x:v>
@@ -2429,1141 +2396,1141 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C59" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E65" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D65" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E65" s="0" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D66" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E66" s="0" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C75" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C79" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D79" s="0" t="s">
+      <x:c r="E79" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="E79" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C80" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
+      <x:c r="E80" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="E80" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C82" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D82" s="0" t="s">
+      <x:c r="E82" s="0" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="E82" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D83" s="0" t="s">
+      <x:c r="E83" s="0" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="E83" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C87" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C94" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C95" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C100" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C110" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C117" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C118" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E119" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C119" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D119" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E119" s="0" t="s">
-        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E120" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C120" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D120" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E120" s="0" t="s">
-        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
@@ -3571,16 +3538,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
@@ -3588,16 +3555,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
@@ -3605,50 +3572,50 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D127" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E127" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E128" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B128" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C128" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D128" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E128" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
@@ -3656,16 +3623,16 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C129" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
@@ -3673,166 +3640,166 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C132" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C134" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="B139" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C139" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D139" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
         <x:v>73</x:v>
@@ -3840,16 +3807,16 @@
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="B140" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C140" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D140" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
         <x:v>73</x:v>
@@ -3857,16 +3824,16 @@
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D141" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C141" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D141" s="0" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
         <x:v>73</x:v>
@@ -3874,16 +3841,16 @@
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C142" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
         <x:v>73</x:v>
@@ -3891,16 +3858,16 @@
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C143" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
         <x:v>73</x:v>
@@ -3911,16 +3878,16 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
@@ -3928,16 +3895,16 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
@@ -3948,47 +3915,47 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D147" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E147" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B147" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C147" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D147" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E147" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D148" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E148" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C148" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D148" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E148" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
@@ -3996,16 +3963,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
@@ -4013,356 +3980,288 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C155" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D156" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E156" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="B156" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C156" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D156" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E156" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E157" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="B157" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C157" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D157" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E157" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E158" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="B158" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C158" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D158" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E158" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E159" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="B159" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C159" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D159" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E159" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D160" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E160" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="B160" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C160" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D160" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E160" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E161" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="B161" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C161" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D161" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E161" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="E164" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C165" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E165" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E166" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" spans="1:11">
-      <x:c r="A167" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B167" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C167" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D167" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E167" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168" spans="1:11">
-      <x:c r="A168" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B168" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C168" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D168" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E168" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" spans="1:11">
-      <x:c r="A169" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B169" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C169" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D169" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E169" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" spans="1:11">
-      <x:c r="A170" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B170" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C170" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D170" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E170" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -292,6 +292,15 @@
     <x:t>28.04.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
   </x:si>
   <x:si>
@@ -313,13 +322,13 @@
     <x:t>Kredili İşlem Yasağı</x:t>
   </x:si>
   <x:si>
+    <x:t>PBRUT</x:t>
+  </x:si>
+  <x:si>
     <x:t>PYAYN</x:t>
   </x:si>
   <x:si>
     <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PBRUT</x:t>
   </x:si>
   <x:si>
     <x:t>PEIAK</x:t>
@@ -694,7 +703,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K166"/>
+  <x:dimension ref="A1:K179"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -2202,88 +2211,142 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
+    <x:row r="44" spans="1:11">
+      <x:c r="A44" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B44" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C44" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J44" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K44" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B45" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C45" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J45" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K45" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
+      <x:c r="B46" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C46" s="0">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:11">
-      <x:c r="A47" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J46" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K46" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>12</x:v>
@@ -2294,16 +2357,16 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>13</x:v>
@@ -2311,16 +2374,16 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
         <x:v>13</x:v>
@@ -2328,16 +2391,16 @@
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
         <x:v>13</x:v>
@@ -2345,13 +2408,13 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>18</x:v>
@@ -2362,13 +2425,13 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>18</x:v>
@@ -2379,13 +2442,13 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>18</x:v>
@@ -2396,53 +2459,53 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
@@ -2450,10 +2513,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>22</x:v>
@@ -2467,10 +2530,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>22</x:v>
@@ -2484,10 +2547,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>22</x:v>
@@ -2498,16 +2561,16 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
         <x:v>23</x:v>
@@ -2515,16 +2578,16 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
         <x:v>23</x:v>
@@ -2532,16 +2595,16 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
         <x:v>23</x:v>
@@ -2552,10 +2615,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>25</x:v>
@@ -2569,10 +2632,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>25</x:v>
@@ -2586,10 +2649,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>25</x:v>
@@ -2600,13 +2663,13 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>25</x:v>
@@ -2617,13 +2680,13 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>25</x:v>
@@ -2634,13 +2697,13 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>25</x:v>
@@ -2651,13 +2714,13 @@
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>25</x:v>
@@ -2668,16 +2731,16 @@
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
         <x:v>23</x:v>
@@ -2685,16 +2748,16 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
         <x:v>23</x:v>
@@ -2702,16 +2765,16 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
         <x:v>23</x:v>
@@ -2722,10 +2785,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>29</x:v>
@@ -2739,10 +2802,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>29</x:v>
@@ -2756,10 +2819,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>29</x:v>
@@ -2770,186 +2833,186 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C88" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
         <x:v>41</x:v>
@@ -2957,16 +3020,16 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
         <x:v>41</x:v>
@@ -2974,13 +3037,13 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>43</x:v>
@@ -2991,13 +3054,13 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>43</x:v>
@@ -3008,16 +3071,16 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
         <x:v>41</x:v>
@@ -3025,16 +3088,16 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
         <x:v>41</x:v>
@@ -3042,16 +3105,16 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
         <x:v>41</x:v>
@@ -3059,13 +3122,13 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>46</x:v>
@@ -3076,64 +3139,64 @@
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>49</x:v>
@@ -3144,53 +3207,53 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C103" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -3198,10 +3261,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>53</x:v>
@@ -3215,10 +3278,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>53</x:v>
@@ -3232,10 +3295,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>53</x:v>
@@ -3246,64 +3309,64 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>56</x:v>
@@ -3314,13 +3377,13 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>56</x:v>
@@ -3334,10 +3397,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>56</x:v>
@@ -3351,10 +3414,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>56</x:v>
@@ -3368,10 +3431,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>56</x:v>
@@ -3382,13 +3445,13 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>56</x:v>
@@ -3399,13 +3462,13 @@
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>56</x:v>
@@ -3416,13 +3479,13 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>56</x:v>
@@ -3433,13 +3496,13 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>56</x:v>
@@ -3450,67 +3513,67 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
         <x:v>62</x:v>
@@ -3518,16 +3581,16 @@
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
         <x:v>62</x:v>
@@ -3535,67 +3598,67 @@
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
         <x:v>66</x:v>
@@ -3603,16 +3666,16 @@
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
         <x:v>66</x:v>
@@ -3620,13 +3683,13 @@
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>68</x:v>
@@ -3637,13 +3700,13 @@
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>68</x:v>
@@ -3654,13 +3717,13 @@
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>68</x:v>
@@ -3671,13 +3734,13 @@
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>68</x:v>
@@ -3688,64 +3751,64 @@
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>72</x:v>
@@ -3756,13 +3819,13 @@
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>72</x:v>
@@ -3773,13 +3836,13 @@
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>72</x:v>
@@ -3793,10 +3856,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>72</x:v>
@@ -3810,10 +3873,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
         <x:v>72</x:v>
@@ -3827,10 +3890,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
         <x:v>72</x:v>
@@ -3841,13 +3904,13 @@
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
         <x:v>72</x:v>
@@ -3858,13 +3921,13 @@
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
         <x:v>72</x:v>
@@ -3875,64 +3938,64 @@
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
         <x:v>77</x:v>
@@ -3943,13 +4006,13 @@
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>77</x:v>
@@ -3960,87 +4023,87 @@
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
@@ -4048,10 +4111,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>84</x:v>
@@ -4065,10 +4128,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>84</x:v>
@@ -4082,10 +4145,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="C156" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
         <x:v>84</x:v>
@@ -4099,13 +4162,13 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
         <x:v>85</x:v>
@@ -4113,16 +4176,16 @@
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
         <x:v>85</x:v>
@@ -4130,16 +4193,16 @@
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
         <x:v>85</x:v>
@@ -4147,13 +4210,13 @@
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
         <x:v>88</x:v>
@@ -4164,16 +4227,16 @@
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E161" s="0" t="s">
         <x:v>85</x:v>
@@ -4181,16 +4244,16 @@
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
         <x:v>85</x:v>
@@ -4198,13 +4261,13 @@
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>88</x:v>
@@ -4215,13 +4278,13 @@
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>88</x:v>
@@ -4232,16 +4295,16 @@
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E165" s="0" t="s">
         <x:v>85</x:v>
@@ -4249,18 +4312,239 @@
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D166" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E166" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:11">
+      <x:c r="A167" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E167" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:11">
+      <x:c r="A168" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C166" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D166" s="0" t="s">
+      <x:c r="B168" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="E166" s="0" t="s">
+      <x:c r="E168" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:11">
+      <x:c r="A169" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E169" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:11">
+      <x:c r="A170" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E170" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:11">
+      <x:c r="A171" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E171" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:11">
+      <x:c r="A172" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E172" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:11">
+      <x:c r="A173" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E173" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:11">
+      <x:c r="A174" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C174" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D174" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E174" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:11">
+      <x:c r="A175" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C175" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D175" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E175" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:11">
+      <x:c r="A176" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C176" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E176" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:11">
+      <x:c r="A177" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C177" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D177" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E177" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:11">
+      <x:c r="A178" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C178" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D178" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E178" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:11">
+      <x:c r="A179" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C179" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D179" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E179" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,258 +49,243 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.03.2026</x:t>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
     <x:t>29.04.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YIGIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
     <x:t>EGPRO</x:t>
   </x:si>
   <x:si>
     <x:t>GRNYO</x:t>
   </x:si>
   <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
   </x:si>
   <x:si>
@@ -310,6 +295,27 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBRUT</x:t>
+  </x:si>
+  <x:si>
     <x:t>PASKI</x:t>
   </x:si>
   <x:si>
@@ -320,27 +326,6 @@
   </x:si>
   <x:si>
     <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PBRUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
   <x:si>
     <x:t>06.04.2026</x:t>
@@ -703,7 +688,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K179"/>
+  <x:dimension ref="A1:K170"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -761,10 +746,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
         <x:v>14</x:v>
@@ -778,16 +763,16 @@
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="A3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>13</x:v>
@@ -796,10 +781,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
         <x:v>14</x:v>
@@ -822,28 +807,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
@@ -857,28 +842,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
@@ -892,7 +877,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
         <x:v>13</x:v>
@@ -901,10 +886,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>14</x:v>
@@ -918,7 +903,7 @@
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="0">
         <x:v>0</x:v>
@@ -927,33 +912,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="0">
         <x:v>0</x:v>
@@ -962,33 +947,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -997,33 +982,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="0">
         <x:v>0</x:v>
@@ -1032,33 +1017,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B11" s="0">
         <x:v>0</x:v>
@@ -1067,33 +1052,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B12" s="0">
         <x:v>0</x:v>
@@ -1102,68 +1087,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="0">
         <x:v>0</x:v>
@@ -1172,33 +1157,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="0">
         <x:v>0</x:v>
@@ -1207,63 +1192,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B16" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B16" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
@@ -1277,19 +1262,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
         <x:v>14</x:v>
@@ -1303,7 +1288,7 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="0">
         <x:v>0</x:v>
@@ -1312,33 +1297,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1347,19 +1332,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
         <x:v>14</x:v>
@@ -1373,42 +1358,42 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
+      <x:c r="E20" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B21" s="0">
         <x:v>0</x:v>
@@ -1417,33 +1402,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B22" s="0">
         <x:v>0</x:v>
@@ -1452,28 +1437,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
@@ -1490,60 +1475,60 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -1557,68 +1542,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B27" s="0">
         <x:v>0</x:v>
@@ -1627,28 +1612,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
@@ -1665,51 +1650,51 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
         <x:v>14</x:v>
@@ -1732,103 +1717,103 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B33" s="0">
         <x:v>0</x:v>
@@ -1837,33 +1822,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B34" s="0">
         <x:v>0</x:v>
@@ -1872,33 +1857,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B35" s="0">
         <x:v>0</x:v>
@@ -1907,33 +1892,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B36" s="0">
         <x:v>0</x:v>
@@ -1942,33 +1927,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B37" s="0">
         <x:v>0</x:v>
@@ -1977,33 +1962,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B38" s="0">
         <x:v>0</x:v>
@@ -2012,33 +1997,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B39" s="0">
         <x:v>0</x:v>
@@ -2047,28 +2032,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
@@ -2082,28 +2067,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
@@ -2117,19 +2102,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
         <x:v>14</x:v>
@@ -2143,7 +2128,7 @@
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B42" s="0">
         <x:v>0</x:v>
@@ -2152,33 +2137,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J42" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B43" s="0">
         <x:v>0</x:v>
@@ -2187,155 +2172,101 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I43" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J43" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:11">
-      <x:c r="A44" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B44" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C44" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F44" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G44" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H44" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I44" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J44" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K44" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B45" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C45" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E45" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G45" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H45" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I45" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J45" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K45" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:11">
+      <x:c r="A47" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B46" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C46" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
+      <x:c r="D47" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F46" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G46" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H46" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I46" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J46" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K46" s="0" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>95</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
@@ -2343,10 +2274,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>12</x:v>
@@ -2374,13 +2305,13 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>12</x:v>
@@ -2391,16 +2322,16 @@
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
         <x:v>13</x:v>
@@ -2408,16 +2339,16 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
         <x:v>13</x:v>
@@ -2425,16 +2356,16 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
         <x:v>13</x:v>
@@ -2442,16 +2373,16 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
         <x:v>13</x:v>
@@ -2459,16 +2390,16 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
         <x:v>13</x:v>
@@ -2476,16 +2407,16 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
         <x:v>13</x:v>
@@ -2493,16 +2424,16 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
         <x:v>13</x:v>
@@ -2510,24 +2441,24 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>100</x:v>
@@ -2536,219 +2467,219 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D63" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C64" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D64" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D65" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E69" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D69" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E69" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E70" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D70" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E70" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E71" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E71" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D72" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D73" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>100</x:v>
@@ -2757,151 +2688,151 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>100</x:v>
@@ -2910,180 +2841,180 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E85" s="0" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C85" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D85" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E85" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C86" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D86" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E86" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
@@ -3097,10 +3028,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
@@ -3108,38 +3039,38 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C95" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D96" s="0" t="s">
+      <x:c r="E96" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="E96" s="0" t="s">
-        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>100</x:v>
@@ -3148,10 +3079,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
@@ -3159,72 +3090,72 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B100" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C100" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D100" s="0" t="s">
+      <x:c r="E100" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="E100" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D101" s="0" t="s">
+      <x:c r="E101" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="E101" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>100</x:v>
@@ -3233,49 +3164,49 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E102" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="E102" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C103" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D103" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E103" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="E103" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>100</x:v>
@@ -3284,27 +3215,27 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C106" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
@@ -3312,16 +3243,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
@@ -3329,30 +3260,30 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
         <x:v>54</x:v>
@@ -3360,75 +3291,75 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="C112" s="0" t="s">
-        <x:v>104</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>100</x:v>
@@ -3437,61 +3368,61 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E116" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C116" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D116" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E116" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E117" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="C117" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D117" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E117" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
@@ -3499,38 +3430,38 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>100</x:v>
@@ -3539,32 +3470,32 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C121" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D121" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>100</x:v>
@@ -3573,44 +3504,44 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
@@ -3618,123 +3549,123 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D127" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E127" s="0" t="s">
-        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E128" s="0" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="B128" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C128" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D128" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E128" s="0" t="s">
-        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E129" s="0" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="B129" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C129" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D129" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E129" s="0" t="s">
-        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C131" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>100</x:v>
@@ -3743,32 +3674,32 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>100</x:v>
@@ -3777,44 +3708,44 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E135" s="0" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C135" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D135" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E135" s="0" t="s">
-        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
@@ -3828,10 +3759,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
@@ -3839,38 +3770,38 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E139" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="B139" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C139" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D139" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E139" s="0" t="s">
-        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>100</x:v>
@@ -3879,78 +3810,78 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C141" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
@@ -3958,16 +3889,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
@@ -3975,84 +3906,84 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E147" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="E147" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E148" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="E148" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E149" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="E149" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E150" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="E150" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
@@ -4066,83 +3997,83 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E151" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="E151" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D152" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B152" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C152" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D152" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C153" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D153" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D155" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B155" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C155" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D155" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>100</x:v>
@@ -4151,129 +4082,129 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E161" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
@@ -4287,10 +4218,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E164" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
@@ -4298,72 +4229,72 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E165" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E166" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C167" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E167" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C168" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E168" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>100</x:v>
@@ -4372,180 +4303,27 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E169" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C170" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E170" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" spans="1:11">
-      <x:c r="A171" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B171" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C171" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D171" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E171" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" spans="1:11">
-      <x:c r="A172" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B172" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C172" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D172" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E172" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" spans="1:11">
-      <x:c r="A173" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B173" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C173" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D173" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E173" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" spans="1:11">
-      <x:c r="A174" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B174" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="C174" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D174" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E174" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" spans="1:11">
-      <x:c r="A175" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B175" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C175" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D175" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E175" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" spans="1:11">
-      <x:c r="A176" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B176" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C176" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D176" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E176" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177" spans="1:11">
-      <x:c r="A177" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B177" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C177" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D177" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E177" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178" spans="1:11">
-      <x:c r="A178" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B178" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C178" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D178" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E178" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" spans="1:11">
-      <x:c r="A179" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B179" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C179" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D179" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E179" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,240 +49,216 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.04.2026</x:t>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
   </x:si>
   <x:si>
     <x:t>30.04.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YIGIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
     <x:t>ULUSE</x:t>
   </x:si>
   <x:si>
@@ -295,6 +271,24 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PKISY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kredili İşlem Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açığa Satış Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBRUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.04.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>PPEGK</x:t>
   </x:si>
   <x:si>
@@ -311,24 +305,6 @@
   </x:si>
   <x:si>
     <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PBRUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKISY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>16.04.2026</x:t>
@@ -688,7 +664,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K170"/>
+  <x:dimension ref="A1:K143"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -752,18 +728,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="A3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="0">
         <x:v>0</x:v>
@@ -772,13 +748,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>14</x:v>
@@ -787,18 +763,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="0">
         <x:v>0</x:v>
@@ -807,13 +783,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>14</x:v>
@@ -822,18 +798,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>0</x:v>
@@ -842,13 +818,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>14</x:v>
@@ -857,18 +833,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -877,13 +853,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
         <x:v>14</x:v>
@@ -892,18 +868,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="0">
         <x:v>0</x:v>
@@ -912,13 +888,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>14</x:v>
@@ -927,18 +903,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B8" s="0">
         <x:v>0</x:v>
@@ -947,13 +923,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
         <x:v>14</x:v>
@@ -962,18 +938,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -985,10 +961,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>14</x:v>
@@ -997,13 +973,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -1023,7 +999,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
         <x:v>14</x:v>
@@ -1032,13 +1008,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
@@ -1052,13 +1028,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>14</x:v>
@@ -1067,33 +1043,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
         <x:v>14</x:v>
@@ -1102,18 +1078,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B13" s="0">
         <x:v>0</x:v>
@@ -1122,13 +1098,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>14</x:v>
@@ -1137,33 +1113,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>14</x:v>
@@ -1172,33 +1148,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
         <x:v>14</x:v>
@@ -1207,13 +1183,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
@@ -1227,13 +1203,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
         <x:v>14</x:v>
@@ -1242,13 +1218,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
@@ -1262,11 +1238,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -1277,33 +1253,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>14</x:v>
@@ -1312,18 +1288,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1332,7 +1308,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
         <x:v>49</x:v>
@@ -1347,33 +1323,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="B20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
         <x:v>14</x:v>
@@ -1382,13 +1358,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
@@ -1402,13 +1378,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
         <x:v>14</x:v>
@@ -1417,13 +1393,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -1437,13 +1413,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
         <x:v>14</x:v>
@@ -1452,33 +1428,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
+      <x:c r="E23" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
         <x:v>14</x:v>
@@ -1487,13 +1463,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -1507,10 +1483,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>14</x:v>
@@ -1522,18 +1498,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B25" s="0">
         <x:v>0</x:v>
@@ -1542,13 +1518,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
         <x:v>14</x:v>
@@ -1557,18 +1533,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B26" s="0">
         <x:v>0</x:v>
@@ -1580,10 +1556,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
         <x:v>14</x:v>
@@ -1592,13 +1568,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
@@ -1615,10 +1591,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
         <x:v>14</x:v>
@@ -1627,13 +1603,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
@@ -1653,7 +1629,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
         <x:v>14</x:v>
@@ -1662,13 +1638,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
@@ -1682,10 +1658,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>14</x:v>
@@ -1708,7 +1684,7 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B30" s="0">
         <x:v>0</x:v>
@@ -1717,13 +1693,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
         <x:v>14</x:v>
@@ -1732,18 +1708,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B31" s="0">
         <x:v>0</x:v>
@@ -1752,13 +1728,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
         <x:v>14</x:v>
@@ -1767,33 +1743,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
         <x:v>14</x:v>
@@ -1802,18 +1778,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B33" s="0">
         <x:v>0</x:v>
@@ -1822,13 +1798,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
         <x:v>14</x:v>
@@ -1837,13 +1813,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
@@ -1860,10 +1836,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
         <x:v>14</x:v>
@@ -1872,18 +1848,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B35" s="0">
         <x:v>0</x:v>
@@ -1892,13 +1868,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
         <x:v>14</x:v>
@@ -1907,18 +1883,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B36" s="0">
         <x:v>0</x:v>
@@ -1927,13 +1903,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
         <x:v>14</x:v>
@@ -1942,18 +1918,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B37" s="0">
         <x:v>0</x:v>
@@ -1965,10 +1941,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
         <x:v>14</x:v>
@@ -1977,18 +1953,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B38" s="0">
         <x:v>0</x:v>
@@ -1997,13 +1973,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
         <x:v>14</x:v>
@@ -2012,1133 +1988,1043 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:11">
-      <x:c r="A39" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B39" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G39" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H39" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I39" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J39" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K39" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B40" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C40" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E40" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F40" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G40" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H40" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I40" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J40" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K40" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C41" s="0">
-        <x:v>0</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K41" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B42" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C42" s="0">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F42" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G42" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H42" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I42" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J42" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K42" s="0" t="s">
-        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:11">
+      <x:c r="A44" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B43" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C43" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F43" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G43" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H43" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I43" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J43" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K43" s="0" t="s">
-        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>95</x:v>
@@ -3147,593 +3033,593 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>95</x:v>
@@ -3742,588 +3628,129 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="144" spans="1:11">
-      <x:c r="A144" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B144" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C144" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D144" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E144" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" spans="1:11">
-      <x:c r="A145" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B145" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C145" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D145" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E145" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146" spans="1:11">
-      <x:c r="A146" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B146" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C146" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D146" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E146" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="147" spans="1:11">
-      <x:c r="A147" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B147" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C147" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D147" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E147" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148" spans="1:11">
-      <x:c r="A148" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C148" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D148" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E148" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="149" spans="1:11">
-      <x:c r="A149" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C149" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D149" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E149" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="150" spans="1:11">
-      <x:c r="A150" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B150" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C150" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D150" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E150" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="151" spans="1:11">
-      <x:c r="A151" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B151" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C151" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D151" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E151" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="152" spans="1:11">
-      <x:c r="A152" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B152" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C152" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D152" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E152" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="153" spans="1:11">
-      <x:c r="A153" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C153" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D153" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E153" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="154" spans="1:11">
-      <x:c r="A154" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B154" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C154" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D154" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E154" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="155" spans="1:11">
-      <x:c r="A155" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B155" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C155" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D155" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E155" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="156" spans="1:11">
-      <x:c r="A156" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B156" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C156" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D156" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E156" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157" spans="1:11">
-      <x:c r="A157" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B157" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C157" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D157" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E157" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158" spans="1:11">
-      <x:c r="A158" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B158" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C158" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D158" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E158" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" spans="1:11">
-      <x:c r="A159" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B159" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C159" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D159" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E159" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" spans="1:11">
-      <x:c r="A160" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B160" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C160" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D160" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E160" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" spans="1:11">
-      <x:c r="A161" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B161" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C161" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D161" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E161" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" spans="1:11">
-      <x:c r="A162" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B162" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C162" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D162" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E162" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163" spans="1:11">
-      <x:c r="A163" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B163" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C163" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D163" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E163" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164" spans="1:11">
-      <x:c r="A164" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B164" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C164" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D164" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E164" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165" spans="1:11">
-      <x:c r="A165" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B165" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C165" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D165" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E165" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166" spans="1:11">
-      <x:c r="A166" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C166" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D166" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E166" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" spans="1:11">
-      <x:c r="A167" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B167" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C167" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D167" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E167" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168" spans="1:11">
-      <x:c r="A168" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B168" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C168" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D168" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E168" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" spans="1:11">
-      <x:c r="A169" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B169" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C169" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D169" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E169" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" spans="1:11">
-      <x:c r="A170" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B170" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C170" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D170" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E170" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -130,136 +130,142 @@
     <x:t>13.05.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>BORLS</x:t>
   </x:si>
   <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
+    <x:t>04.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
   </x:si>
   <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
@@ -271,18 +277,18 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PASKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açığa Satış Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PKISY</x:t>
   </x:si>
   <x:si>
     <x:t>Kredili İşlem Yasağı</x:t>
   </x:si>
   <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
-  </x:si>
-  <x:si>
     <x:t>PBRUT</x:t>
   </x:si>
   <x:si>
@@ -295,16 +301,16 @@
     <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
   <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
     <x:t>PEIAK</x:t>
   </x:si>
   <x:si>
     <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
   </x:si>
   <x:si>
     <x:t>16.04.2026</x:t>
@@ -664,7 +670,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K143"/>
+  <x:dimension ref="A1:K151"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1104,7 +1110,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>14</x:v>
@@ -1113,13 +1119,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
@@ -1139,7 +1145,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>14</x:v>
@@ -1148,13 +1154,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
@@ -1203,13 +1209,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
         <x:v>14</x:v>
@@ -1229,22 +1235,22 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B17" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B17" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
         <x:v>14</x:v>
@@ -1264,7 +1270,7 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="0">
         <x:v>0</x:v>
@@ -1273,13 +1279,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>14</x:v>
@@ -1299,22 +1305,22 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B19" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C19" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B19" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C19" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
         <x:v>14</x:v>
@@ -1334,19 +1340,19 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>15</x:v>
@@ -1378,10 +1384,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>15</x:v>
@@ -1413,10 +1419,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>15</x:v>
@@ -1431,7 +1437,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
         <x:v>15</x:v>
@@ -1439,22 +1445,22 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
+      <x:c r="E23" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
         <x:v>14</x:v>
@@ -1463,13 +1469,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -1483,13 +1489,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
         <x:v>14</x:v>
@@ -1498,13 +1504,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -1518,10 +1524,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>15</x:v>
@@ -1536,7 +1542,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
         <x:v>15</x:v>
@@ -1544,20 +1550,20 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
+      <x:c r="E26" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1571,7 +1577,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
         <x:v>15</x:v>
@@ -1588,10 +1594,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>15</x:v>
@@ -1614,7 +1620,7 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B28" s="0">
         <x:v>0</x:v>
@@ -1623,13 +1629,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
         <x:v>14</x:v>
@@ -1638,18 +1644,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B29" s="0">
         <x:v>0</x:v>
@@ -1658,11 +1664,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -1673,13 +1679,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
@@ -1693,13 +1699,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
         <x:v>14</x:v>
@@ -1719,19 +1725,19 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
         <x:v>15</x:v>
@@ -1763,10 +1769,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>15</x:v>
@@ -1789,7 +1795,7 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B33" s="0">
         <x:v>0</x:v>
@@ -1798,10 +1804,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>15</x:v>
@@ -1824,19 +1830,19 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
         <x:v>15</x:v>
@@ -1868,13 +1874,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
         <x:v>14</x:v>
@@ -1883,13 +1889,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
@@ -1903,13 +1909,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
         <x:v>14</x:v>
@@ -1918,30 +1924,30 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>15</x:v>
@@ -1973,13 +1979,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
         <x:v>14</x:v>
@@ -1997,31 +2003,49 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:11">
-      <x:c r="A40" s="0" t="s">
+    <x:row r="39" spans="1:11">
+      <x:c r="A39" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
         <x:v>82</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J39" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K39" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>85</x:v>
@@ -2030,10 +2054,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
@@ -2061,10 +2085,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
         <x:v>13</x:v>
@@ -2072,19 +2096,19 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
@@ -2092,10 +2116,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>17</x:v>
@@ -2106,19 +2130,19 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
@@ -2126,10 +2150,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>20</x:v>
@@ -2140,7 +2164,7 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>87</x:v>
@@ -2149,10 +2173,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
@@ -2160,10 +2184,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>23</x:v>
@@ -2177,13 +2201,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>24</x:v>
@@ -2191,13 +2215,13 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>26</x:v>
@@ -2225,13 +2249,13 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>26</x:v>
@@ -2259,16 +2283,16 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
         <x:v>24</x:v>
@@ -2279,10 +2303,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>29</x:v>
@@ -2293,13 +2317,13 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>29</x:v>
@@ -2313,10 +2337,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>29</x:v>
@@ -2327,19 +2351,19 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
@@ -2347,10 +2371,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>32</x:v>
@@ -2361,13 +2385,13 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>32</x:v>
@@ -2381,10 +2405,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>32</x:v>
@@ -2395,19 +2419,19 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
@@ -2432,10 +2456,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>36</x:v>
@@ -2449,10 +2473,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>36</x:v>
@@ -2466,10 +2490,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>36</x:v>
@@ -2483,10 +2507,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>36</x:v>
@@ -2497,7 +2521,7 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>87</x:v>
@@ -2506,10 +2530,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
@@ -2517,10 +2541,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>39</x:v>
@@ -2531,13 +2555,13 @@
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>39</x:v>
@@ -2548,13 +2572,13 @@
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>39</x:v>
@@ -2565,13 +2589,13 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>39</x:v>
@@ -2582,13 +2606,13 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>39</x:v>
@@ -2599,13 +2623,13 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>39</x:v>
@@ -2633,13 +2657,13 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>39</x:v>
@@ -2667,13 +2691,13 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>39</x:v>
@@ -2687,72 +2711,72 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D83" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E83" s="0" t="s">
-        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>87</x:v>
@@ -2761,100 +2785,100 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E88" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C88" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D88" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E88" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E89" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D90" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>87</x:v>
@@ -2863,27 +2887,27 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
@@ -2891,33 +2915,33 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
@@ -2925,152 +2949,152 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D96" s="0" t="s">
+      <x:c r="E96" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E96" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D97" s="0" t="s">
+      <x:c r="E97" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E97" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D98" s="0" t="s">
+      <x:c r="E98" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E98" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E99" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E99" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E100" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E100" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E101" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E101" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E102" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E102" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E103" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E103" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -3078,33 +3102,33 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E104" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E104" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E105" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E105" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
@@ -3112,55 +3136,55 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B107" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D107" s="0" t="s">
+      <x:c r="E107" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="E107" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B108" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D108" s="0" t="s">
+      <x:c r="E108" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="E108" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>87</x:v>
@@ -3169,27 +3193,27 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E109" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="E109" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E110" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="E110" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
@@ -3203,49 +3227,49 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C112" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D112" s="0" t="s">
+      <x:c r="E112" s="0" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="E112" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>95</x:v>
@@ -3254,146 +3278,146 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E114" s="0" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="E114" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C115" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D115" s="0" t="s">
+      <x:c r="E115" s="0" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="E115" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C116" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D116" s="0" t="s">
+      <x:c r="E116" s="0" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="E116" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C117" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D117" s="0" t="s">
+      <x:c r="E117" s="0" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="E117" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C118" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D118" s="0" t="s">
+      <x:c r="E118" s="0" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="E118" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E119" s="0" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="E119" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
@@ -3404,18 +3428,18 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>87</x:v>
@@ -3424,32 +3448,32 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B125" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C125" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D125" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>87</x:v>
@@ -3458,10 +3482,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
@@ -3469,38 +3493,38 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B128" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C128" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D128" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>87</x:v>
@@ -3509,49 +3533,49 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C130" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D130" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C131" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D131" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>87</x:v>
@@ -3560,10 +3584,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
@@ -3571,55 +3595,55 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>95</x:v>
@@ -3628,44 +3652,44 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
@@ -3673,67 +3697,67 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B140" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C140" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D140" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D141" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C141" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D141" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
@@ -3741,16 +3765,152 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:11">
+      <x:c r="A144" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D144" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E144" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:11">
+      <x:c r="A145" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E145" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:11">
+      <x:c r="A146" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D146" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E146" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:11">
+      <x:c r="A147" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D147" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E147" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:11">
+      <x:c r="A148" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D148" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E148" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:11">
+      <x:c r="A149" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E149" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:11">
+      <x:c r="A150" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E150" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:11">
+      <x:c r="A151" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D151" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E151" s="0" t="s">
+        <x:v>82</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,223 +49,226 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.03.2026</x:t>
+    <x:t>ADEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
   </x:si>
   <x:si>
     <x:t>05.05.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>ICUGS</x:t>
   </x:si>
   <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YIGIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
+    <x:t>05.06.2026</x:t>
   </x:si>
   <x:si>
     <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
   </x:si>
   <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
@@ -277,22 +280,19 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PKISY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kredili İşlem Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PASKI</x:t>
   </x:si>
   <x:si>
     <x:t>Açığa Satış Yasağı</x:t>
   </x:si>
   <x:si>
-    <x:t>PKISY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
     <x:t>PBRUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>PPEGK</x:t>
@@ -670,7 +670,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K151"/>
+  <x:dimension ref="A1:K159"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -728,19 +728,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -760,22 +760,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
@@ -798,19 +798,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
@@ -827,65 +827,65 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="0">
         <x:v>0</x:v>
@@ -894,63 +894,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="E8" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
@@ -964,28 +964,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -1008,10 +1008,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
         <x:v>15</x:v>
@@ -1034,19 +1034,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
         <x:v>15</x:v>
@@ -1060,28 +1060,28 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
+      <x:c r="E12" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
         <x:v>14</x:v>
@@ -1104,19 +1104,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
         <x:v>14</x:v>
@@ -1130,7 +1130,7 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="0">
         <x:v>0</x:v>
@@ -1139,7 +1139,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>40</x:v>
@@ -1148,54 +1148,54 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
@@ -1209,28 +1209,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
@@ -1250,22 +1250,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
@@ -1279,33 +1279,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1314,33 +1314,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B20" s="0">
         <x:v>0</x:v>
@@ -1352,25 +1352,25 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
@@ -1387,16 +1387,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
         <x:v>15</x:v>
@@ -1419,60 +1419,60 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
         <x:v>14</x:v>
@@ -1489,28 +1489,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -1530,22 +1530,22 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -1559,19 +1559,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
         <x:v>15</x:v>
@@ -1585,7 +1585,7 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B27" s="0">
         <x:v>0</x:v>
@@ -1594,28 +1594,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
@@ -1632,16 +1632,16 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
         <x:v>14</x:v>
@@ -1655,7 +1655,7 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B29" s="0">
         <x:v>0</x:v>
@@ -1664,98 +1664,98 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
@@ -1769,19 +1769,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
         <x:v>15</x:v>
@@ -1795,42 +1795,42 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B34" s="0">
         <x:v>0</x:v>
@@ -1839,54 +1839,54 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
         <x:v>14</x:v>
@@ -1912,16 +1912,16 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
         <x:v>15</x:v>
@@ -1944,63 +1944,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B38" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B38" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C38" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
@@ -2017,16 +2017,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
         <x:v>14</x:v>
@@ -2038,43 +2038,61 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:11">
-      <x:c r="A41" s="0" t="s">
+    <x:row r="40" spans="1:11">
+      <x:c r="A40" s="0" t="s">
         <x:v>84</x:v>
+      </x:c>
+      <x:c r="B40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K40" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -2082,10 +2100,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>12</x:v>
@@ -2099,13 +2117,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
         <x:v>13</x:v>
@@ -2116,10 +2134,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>17</x:v>
@@ -2133,10 +2151,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>17</x:v>
@@ -2150,10 +2168,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>20</x:v>
@@ -2167,10 +2185,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>20</x:v>
@@ -2181,19 +2199,19 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
@@ -2201,16 +2219,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
@@ -2218,118 +2236,118 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D57" s="0" t="s">
+      <x:c r="E57" s="0" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="E57" s="0" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D58" s="0" t="s">
+      <x:c r="E58" s="0" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="E58" s="0" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
@@ -2337,16 +2355,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="E59" s="0" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
@@ -2354,16 +2372,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="E60" s="0" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
@@ -2371,10 +2389,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>32</x:v>
@@ -2388,10 +2406,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>32</x:v>
@@ -2402,13 +2420,13 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>32</x:v>
@@ -2419,13 +2437,13 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>32</x:v>
@@ -2436,109 +2454,109 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D67" s="0" t="s">
+      <x:c r="E67" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="E67" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D68" s="0" t="s">
+      <x:c r="E68" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="E68" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D69" s="0" t="s">
+      <x:c r="E69" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="E69" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D70" s="0" t="s">
+      <x:c r="E70" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="E70" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>95</x:v>
@@ -2547,61 +2565,61 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
@@ -2609,16 +2627,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
@@ -2626,30 +2644,30 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
         <x:v>40</x:v>
@@ -2657,16 +2675,16 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
         <x:v>40</x:v>
@@ -2674,16 +2692,16 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
         <x:v>40</x:v>
@@ -2691,16 +2709,16 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C80" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
         <x:v>40</x:v>
@@ -2708,19 +2726,19 @@
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
@@ -2728,13 +2746,13 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
         <x:v>44</x:v>
@@ -2745,13 +2763,13 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
         <x:v>44</x:v>
@@ -2759,13 +2777,13 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>46</x:v>
@@ -2779,10 +2797,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>46</x:v>
@@ -2793,19 +2811,19 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
@@ -2813,16 +2831,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
@@ -2830,101 +2848,101 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
@@ -2932,55 +2950,55 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>97</x:v>
@@ -2989,129 +3007,129 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C100" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E102" s="0" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="B102" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D102" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E102" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E103" s="0" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="B103" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C103" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D103" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E103" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
@@ -3119,33 +3137,33 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
@@ -3153,10 +3171,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>59</x:v>
@@ -3170,10 +3188,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>59</x:v>
@@ -3187,16 +3205,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
@@ -3204,152 +3222,152 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B111" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C111" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D111" s="0" t="s">
+      <x:c r="E111" s="0" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="E111" s="0" t="s">
-        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C112" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D112" s="0" t="s">
+      <x:c r="E112" s="0" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="E112" s="0" t="s">
-        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C116" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
@@ -3357,135 +3375,135 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B123" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C123" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D123" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C124" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D124" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B125" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C125" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D125" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C126" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D126" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
@@ -3493,16 +3511,16 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
@@ -3510,203 +3528,203 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C134" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E137" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="B137" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C137" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D137" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E137" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D138" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E138" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="B138" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C138" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D138" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E138" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
@@ -3714,203 +3732,339 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C144" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:11">
+      <x:c r="A152" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D152" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E152" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:11">
+      <x:c r="A153" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E153" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:11">
+      <x:c r="A154" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D154" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E154" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:11">
+      <x:c r="A155" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D155" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E155" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:11">
+      <x:c r="A156" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D156" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E156" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:11">
+      <x:c r="A157" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E157" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:11">
+      <x:c r="A158" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E158" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:11">
+      <x:c r="A159" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E159" s="0" t="s">
+        <x:v>81</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,228 +49,225 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>ADEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.04.2026</x:t>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
   </x:si>
   <x:si>
     <x:t>06.05.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YIGIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
     <x:t>SEYKM</x:t>
   </x:si>
   <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
   </x:si>
   <x:si>
@@ -280,16 +277,16 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PASKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açığa Satış Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PKISY</x:t>
   </x:si>
   <x:si>
     <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
   </x:si>
   <x:si>
     <x:t>PBRUT</x:t>
@@ -748,10 +745,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>0</x:v>
+        <x:v>19.37</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>0</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -760,7 +757,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>15</x:v>
@@ -792,10 +789,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>15</x:v>
@@ -815,19 +812,19 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>14</x:v>
@@ -850,7 +847,7 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -859,10 +856,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>14</x:v>
@@ -885,7 +882,7 @@
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="0">
         <x:v>0</x:v>
@@ -897,7 +894,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>14</x:v>
@@ -929,10 +926,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>14</x:v>
@@ -955,22 +952,22 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>15</x:v>
@@ -979,13 +976,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -1034,13 +1031,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>15</x:v>
@@ -1049,18 +1046,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B12" s="0">
         <x:v>0</x:v>
@@ -1069,10 +1066,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>14</x:v>
@@ -1095,7 +1092,7 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="0">
         <x:v>0</x:v>
@@ -1104,13 +1101,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>15</x:v>
@@ -1130,22 +1127,22 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>15</x:v>
@@ -1165,22 +1162,22 @@
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
         <x:v>15</x:v>
@@ -1200,22 +1197,22 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B16" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B16" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
         <x:v>15</x:v>
@@ -1235,7 +1232,7 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1244,10 +1241,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>14</x:v>
@@ -1270,7 +1267,7 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="0">
         <x:v>0</x:v>
@@ -1279,10 +1276,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>14</x:v>
@@ -1305,20 +1302,20 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B19" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C19" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B19" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C19" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -1332,7 +1329,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
         <x:v>14</x:v>
@@ -1349,13 +1346,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
         <x:v>15</x:v>
@@ -1364,18 +1361,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B21" s="0">
         <x:v>0</x:v>
@@ -1384,13 +1381,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
         <x:v>15</x:v>
@@ -1399,31 +1396,31 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -1437,7 +1434,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
         <x:v>14</x:v>
@@ -1454,10 +1451,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>14</x:v>
@@ -1472,7 +1469,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
         <x:v>14</x:v>
@@ -1480,19 +1477,19 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="B24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>14</x:v>
@@ -1530,7 +1527,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
         <x:v>15</x:v>
@@ -1539,13 +1536,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -1559,10 +1556,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>15</x:v>
@@ -1574,18 +1571,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B27" s="0">
         <x:v>0</x:v>
@@ -1594,13 +1591,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
         <x:v>15</x:v>
@@ -1620,7 +1617,7 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B28" s="0">
         <x:v>0</x:v>
@@ -1629,10 +1626,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>14</x:v>
@@ -1655,7 +1652,7 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B29" s="0">
         <x:v>0</x:v>
@@ -1667,7 +1664,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>14</x:v>
@@ -1690,19 +1687,19 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
         <x:v>14</x:v>
@@ -1725,7 +1722,7 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B31" s="0">
         <x:v>0</x:v>
@@ -1734,13 +1731,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
         <x:v>15</x:v>
@@ -1749,18 +1746,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B32" s="0">
         <x:v>0</x:v>
@@ -1772,10 +1769,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
         <x:v>15</x:v>
@@ -1784,18 +1781,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B33" s="0">
         <x:v>0</x:v>
@@ -1804,10 +1801,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>14</x:v>
@@ -1830,22 +1827,22 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>0</x:v>
+        <x:v>7.14</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>0</x:v>
+        <x:v>-9.96</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
         <x:v>15</x:v>
@@ -1865,19 +1862,19 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>15</x:v>
@@ -1889,31 +1886,31 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="F36" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1924,18 +1921,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B37" s="0">
         <x:v>0</x:v>
@@ -1944,10 +1941,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>15</x:v>
@@ -1970,7 +1967,7 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B38" s="0">
         <x:v>0</x:v>
@@ -1979,13 +1976,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
         <x:v>15</x:v>
@@ -2005,7 +2002,7 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B39" s="0">
         <x:v>0</x:v>
@@ -2014,13 +2011,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
         <x:v>15</x:v>
@@ -2029,18 +2026,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B40" s="0">
         <x:v>0</x:v>
@@ -2052,10 +2049,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
         <x:v>15</x:v>
@@ -2064,18 +2061,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
@@ -2083,10 +2080,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>3</x:v>
@@ -2100,10 +2097,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>12</x:v>
@@ -2117,10 +2114,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>12</x:v>
@@ -2134,10 +2131,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>17</x:v>
@@ -2151,10 +2148,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>17</x:v>
@@ -2165,19 +2162,19 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
@@ -2185,16 +2182,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
@@ -2202,118 +2199,118 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D51" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D52" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
@@ -2321,16 +2318,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
@@ -2338,118 +2335,118 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C59" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D59" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E59" s="0" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D60" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E60" s="0" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
@@ -2457,10 +2454,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>32</x:v>
@@ -2474,10 +2471,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>32</x:v>
@@ -2488,70 +2485,70 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
@@ -2559,16 +2556,16 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
@@ -2576,339 +2573,339 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C75" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C76" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B78" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C78" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D78" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C79" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D79" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C80" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E80" s="0" t="s">
-        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C81" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D81" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E81" s="0" t="s">
-        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C82" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D82" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D83" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C84" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E89" s="0" t="s">
-        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D90" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E90" s="0" t="s">
-        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C91" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
@@ -2916,16 +2913,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C92" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
@@ -2933,169 +2930,169 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C93" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C95" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C99" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E100" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="B100" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C100" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D100" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E100" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E101" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D101" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E101" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
@@ -3103,16 +3100,16 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -3120,50 +3117,50 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E105" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="B105" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C105" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D105" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E105" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E106" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="B106" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C106" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D106" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E106" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
@@ -3171,10 +3168,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>59</x:v>
@@ -3188,10 +3185,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>59</x:v>
@@ -3202,87 +3199,87 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
@@ -3290,16 +3287,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C114" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C114" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
@@ -3307,764 +3304,764 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C117" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C121" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="C122" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B123" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C123" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D123" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C124" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D124" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C125" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C128" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C130" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C135" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D135" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E135" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="E135" s="0" t="s">
-        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C136" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D136" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E136" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="E136" s="0" t="s">
-        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B137" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C137" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D137" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D138" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B138" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C138" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D138" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B139" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C139" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D139" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D144" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E144" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B144" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C144" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D144" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E144" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E145" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B145" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C145" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D145" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E145" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C147" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C150" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C152" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C153" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,223 +49,226 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>MARTI</x:t>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
   </x:si>
   <x:si>
     <x:t>08.04.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
     <x:t>07.05.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YIGIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
   </x:si>
   <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
@@ -298,16 +301,16 @@
     <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
   <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PYAYN</x:t>
   </x:si>
   <x:si>
     <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
   </x:si>
   <x:si>
     <x:t>16.04.2026</x:t>
@@ -667,7 +670,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K159"/>
+  <x:dimension ref="A1:K162"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -725,19 +728,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -745,74 +748,74 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>19.37</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>2.16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>0</x:v>
@@ -821,33 +824,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -859,25 +862,25 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -891,54 +894,54 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
         <x:v>14</x:v>
@@ -967,22 +970,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -996,19 +999,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
         <x:v>15</x:v>
@@ -1022,7 +1025,7 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="0">
         <x:v>0</x:v>
@@ -1031,63 +1034,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
@@ -1101,28 +1104,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
@@ -1136,28 +1139,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
@@ -1171,28 +1174,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
@@ -1206,33 +1209,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1241,95 +1244,95 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B19" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C19" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B19" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C19" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
         <x:v>14</x:v>
@@ -1337,7 +1340,7 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="0">
         <x:v>0</x:v>
@@ -1346,19 +1349,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
         <x:v>15</x:v>
@@ -1372,112 +1375,112 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B21" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C21" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B21" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C21" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B24" s="0">
         <x:v>0</x:v>
@@ -1486,19 +1489,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
         <x:v>14</x:v>
@@ -1512,28 +1515,28 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
         <x:v>15</x:v>
@@ -1547,37 +1550,37 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
@@ -1591,63 +1594,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B28" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B28" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C28" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
@@ -1664,25 +1667,25 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
@@ -1696,19 +1699,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
         <x:v>14</x:v>
@@ -1722,28 +1725,28 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
         <x:v>15</x:v>
@@ -1766,63 +1769,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
@@ -1830,25 +1833,25 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>7.14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>-9.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
         <x:v>14</x:v>
@@ -1871,19 +1874,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
         <x:v>15</x:v>
@@ -1906,63 +1909,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
@@ -1976,19 +1979,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
         <x:v>14</x:v>
@@ -2002,28 +2005,28 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B39" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
         <x:v>15</x:v>
@@ -2049,64 +2052,82 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:11">
-      <x:c r="A42" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:11">
+      <x:c r="A41" s="0" t="s">
         <x:v>84</x:v>
+      </x:c>
+      <x:c r="B41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K41" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
@@ -2114,10 +2135,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>12</x:v>
@@ -2128,36 +2149,36 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
@@ -2165,135 +2186,135 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
@@ -2301,135 +2322,135 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E58" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D58" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E58" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
@@ -2437,10 +2458,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>29</x:v>
@@ -2451,87 +2472,87 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
@@ -2539,118 +2560,118 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E74" s="0" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C74" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D74" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E74" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
@@ -2658,33 +2679,33 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C77" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C78" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
@@ -2692,50 +2713,50 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="E79" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
@@ -2743,33 +2764,33 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
@@ -2777,577 +2798,577 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C84" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C86" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C88" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D88" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E89" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D90" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E90" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E91" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="B91" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C91" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D91" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E91" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B99" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C99" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D99" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E100" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="B100" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C100" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D100" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E100" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E101" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D101" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E101" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E102" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="B102" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D102" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E102" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C104" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D104" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B104" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C104" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D104" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E105" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="B105" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C105" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D105" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E105" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E107" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B107" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D107" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E107" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E108" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B108" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D108" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E108" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E109" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B109" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C109" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D109" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E109" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E110" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B110" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C110" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D110" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E110" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E111" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B111" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C111" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D111" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E111" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E112" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C112" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D112" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E112" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E113" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C113" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D113" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E113" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C115" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D115" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C116" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D116" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
@@ -3355,67 +3376,67 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C119" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C120" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D120" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C121" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
@@ -3423,33 +3444,33 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C123" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
@@ -3457,135 +3478,135 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C130" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D130" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C131" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
@@ -3593,84 +3614,84 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C133" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E134" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C134" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D134" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E134" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
@@ -3678,101 +3699,101 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
@@ -3780,50 +3801,50 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C143" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D143" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E143" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="E143" s="0" t="s">
-        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
@@ -3831,84 +3852,84 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C146" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D148" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C148" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D148" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C149" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D149" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
@@ -3916,135 +3937,135 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B157" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C157" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D157" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="E157" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C158" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
@@ -4052,16 +4073,67 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:11">
+      <x:c r="A160" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D160" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E160" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:11">
+      <x:c r="A161" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E161" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:11">
+      <x:c r="A162" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E162" s="0" t="s">
+        <x:v>76</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,228 +49,225 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.03.2026</x:t>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
   </x:si>
   <x:si>
     <x:t>08.05.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YIGIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
     <x:t>DMRGD</x:t>
   </x:si>
   <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
   </x:si>
   <x:si>
@@ -280,37 +277,37 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PKISY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kredili İşlem Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PASKI</x:t>
   </x:si>
   <x:si>
     <x:t>Açığa Satış Yasağı</x:t>
   </x:si>
   <x:si>
-    <x:t>PKISY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kredili İşlem Yasağı</x:t>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
   </x:si>
   <x:si>
     <x:t>PBRUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
   </x:si>
   <x:si>
     <x:t>16.04.2026</x:t>
@@ -670,7 +667,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K162"/>
+  <x:dimension ref="A1:K158"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -728,19 +725,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -754,54 +751,54 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="E4" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>15</x:v>
@@ -824,19 +821,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>15</x:v>
@@ -850,37 +847,37 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="E6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -894,28 +891,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -935,13 +932,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
         <x:v>14</x:v>
@@ -967,16 +964,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
         <x:v>14</x:v>
@@ -990,77 +987,77 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B12" s="0">
         <x:v>0</x:v>
@@ -1072,25 +1069,25 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
@@ -1104,42 +1101,42 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="B14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>39</x:v>
@@ -1148,19 +1145,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
@@ -1174,7 +1171,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>39</x:v>
@@ -1183,10 +1180,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
         <x:v>15</x:v>
@@ -1200,7 +1197,7 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="0">
         <x:v>0</x:v>
@@ -1209,124 +1206,124 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B17" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B17" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B19" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C19" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B19" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C19" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
         <x:v>14</x:v>
@@ -1340,7 +1337,7 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B20" s="0">
         <x:v>0</x:v>
@@ -1349,19 +1346,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
         <x:v>15</x:v>
@@ -1375,7 +1372,7 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B21" s="0">
         <x:v>0</x:v>
@@ -1384,7 +1381,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
         <x:v>51</x:v>
@@ -1393,24 +1390,24 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B22" s="0">
         <x:v>0</x:v>
@@ -1419,33 +1416,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B23" s="0">
         <x:v>0</x:v>
@@ -1457,25 +1454,25 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -1492,16 +1489,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
         <x:v>14</x:v>
@@ -1515,37 +1512,37 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -1559,19 +1556,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
         <x:v>15</x:v>
@@ -1585,37 +1582,37 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
@@ -1629,98 +1626,98 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
@@ -1734,28 +1731,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="F31" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
@@ -1769,28 +1766,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
@@ -1804,28 +1801,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
@@ -1839,98 +1836,98 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
@@ -1944,54 +1941,54 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B38" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B38" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C38" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
         <x:v>14</x:v>
@@ -2005,37 +2002,37 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B39" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
@@ -2049,85 +2046,67 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:11">
-      <x:c r="A41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:11">
+      <x:c r="A42" s="0" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="B41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I41" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J41" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K41" s="0" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>85</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
@@ -2135,10 +2114,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>12</x:v>
@@ -2149,13 +2128,13 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>12</x:v>
@@ -2166,16 +2145,16 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
         <x:v>13</x:v>
@@ -2183,177 +2162,177 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
+      <x:c r="E50" s="0" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="E50" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D51" s="0" t="s">
+      <x:c r="E51" s="0" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="E51" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="E52" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="E53" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
+      <x:c r="E54" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="E54" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D55" s="0" t="s">
+      <x:c r="E55" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="E55" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D56" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E56" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="E56" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D57" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E57" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="E57" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>93</x:v>
@@ -2362,146 +2341,146 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="D66" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
@@ -2509,16 +2488,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
@@ -2526,152 +2505,152 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D70" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E72" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D72" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E72" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E73" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D73" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E73" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
@@ -2679,47 +2658,47 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C79" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D79" s="0" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
         <x:v>39</x:v>
@@ -2727,16 +2706,16 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C80" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
         <x:v>39</x:v>
@@ -2744,16 +2723,16 @@
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C81" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D81" s="0" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
         <x:v>39</x:v>
@@ -2764,13 +2743,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
         <x:v>39</x:v>
@@ -2781,13 +2760,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
         <x:v>39</x:v>
@@ -2795,16 +2774,16 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
         <x:v>39</x:v>
@@ -2812,16 +2791,16 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
         <x:v>39</x:v>
@@ -2829,16 +2808,16 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
         <x:v>39</x:v>
@@ -2846,16 +2825,16 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C87" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
         <x:v>39</x:v>
@@ -2863,189 +2842,189 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E89" s="0" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D90" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E90" s="0" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C93" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B94" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C94" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D94" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B95" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C95" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D95" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
@@ -3053,10 +3032,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>50</x:v>
@@ -3070,10 +3049,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>50</x:v>
@@ -3087,10 +3066,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>50</x:v>
@@ -3101,16 +3080,16 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
         <x:v>51</x:v>
@@ -3121,13 +3100,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
         <x:v>51</x:v>
@@ -3135,104 +3114,104 @@
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
@@ -3240,16 +3219,16 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
@@ -3257,84 +3236,84 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="C111" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C113" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D113" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C114" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D114" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B114" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C114" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D114" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C115" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D115" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
@@ -3342,16 +3321,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
@@ -3359,407 +3338,407 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C126" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D126" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D127" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B128" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C128" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D128" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B129" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C129" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D129" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E133" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="E133" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C134" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C140" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
@@ -3767,16 +3746,16 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
@@ -3784,356 +3763,288 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C147" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C153" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D153" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D154" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B154" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C154" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D154" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D155" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B155" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C155" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D155" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D156" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B156" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C156" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D156" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E157" s="0" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="B157" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C157" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D157" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="E157" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E158" s="0" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="B158" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C158" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D158" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="E158" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" spans="1:11">
-      <x:c r="A159" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B159" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C159" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D159" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E159" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" spans="1:11">
-      <x:c r="A160" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B160" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C160" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D160" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E160" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" spans="1:11">
-      <x:c r="A161" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B161" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C161" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D161" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E161" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" spans="1:11">
-      <x:c r="A162" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B162" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C162" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D162" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E162" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -199,73 +199,82 @@
     <x:t>GRNYO</x:t>
   </x:si>
   <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
+    <x:t>11.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
   </x:si>
   <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
@@ -277,16 +286,19 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PASKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açığa Satış Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PKISY</x:t>
   </x:si>
   <x:si>
     <x:t>Kredili İşlem Yasağı</x:t>
   </x:si>
   <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
+    <x:t>PBRUT</x:t>
   </x:si>
   <x:si>
     <x:t>PEIAK</x:t>
@@ -305,9 +317,6 @@
   </x:si>
   <x:si>
     <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PBRUT</x:t>
   </x:si>
   <x:si>
     <x:t>16.04.2026</x:t>
@@ -667,7 +676,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K158"/>
+  <x:dimension ref="A1:K165"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1626,13 +1635,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
         <x:v>15</x:v>
@@ -1652,20 +1661,20 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1676,18 +1685,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B30" s="0">
         <x:v>0</x:v>
@@ -1696,10 +1705,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
         <x:v>15</x:v>
@@ -1711,30 +1720,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="B31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
         <x:v>15</x:v>
@@ -1766,13 +1775,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
         <x:v>15</x:v>
@@ -1792,22 +1801,22 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
         <x:v>15</x:v>
@@ -1816,13 +1825,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
@@ -1836,13 +1845,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
         <x:v>15</x:v>
@@ -1851,18 +1860,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B35" s="0">
         <x:v>0</x:v>
@@ -1871,10 +1880,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>14</x:v>
@@ -1897,19 +1906,19 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
         <x:v>14</x:v>
@@ -1941,10 +1950,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>14</x:v>
@@ -1967,19 +1976,19 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B38" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B38" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C38" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
+      <x:c r="E38" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>14</x:v>
@@ -2011,10 +2020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
         <x:v>14</x:v>
@@ -2046,13 +2055,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
         <x:v>15</x:v>
@@ -2067,74 +2076,110 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:11">
+      <x:c r="A41" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K41" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B42" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C42" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
-    </x:row>
-    <x:row r="43" spans="1:11">
-      <x:c r="A43" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>4</x:v>
+      <x:c r="F42" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J42" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K42" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>12</x:v>
@@ -2145,13 +2190,13 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>12</x:v>
@@ -2162,36 +2207,36 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
@@ -2199,10 +2244,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>18</x:v>
@@ -2216,10 +2261,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>18</x:v>
@@ -2253,7 +2298,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>18</x:v>
@@ -2264,36 +2309,36 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
@@ -2301,10 +2346,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>21</x:v>
@@ -2318,10 +2363,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>21</x:v>
@@ -2335,10 +2380,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>21</x:v>
@@ -2352,10 +2397,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>21</x:v>
@@ -2366,13 +2411,13 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>21</x:v>
@@ -2383,13 +2428,13 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>21</x:v>
@@ -2400,13 +2445,13 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>21</x:v>
@@ -2417,13 +2462,13 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>21</x:v>
@@ -2434,36 +2479,36 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
@@ -2471,13 +2516,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
         <x:v>27</x:v>
@@ -2485,16 +2530,16 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
         <x:v>27</x:v>
@@ -2502,16 +2547,16 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
         <x:v>27</x:v>
@@ -2519,36 +2564,36 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
@@ -2556,13 +2601,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
         <x:v>32</x:v>
@@ -2570,16 +2615,16 @@
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
         <x:v>32</x:v>
@@ -2587,13 +2632,13 @@
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>34</x:v>
@@ -2604,13 +2649,13 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>34</x:v>
@@ -2621,13 +2666,13 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>34</x:v>
@@ -2638,13 +2683,13 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>34</x:v>
@@ -2655,13 +2700,13 @@
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>34</x:v>
@@ -2672,36 +2717,36 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
@@ -2709,10 +2754,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>38</x:v>
@@ -2723,13 +2768,13 @@
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>38</x:v>
@@ -2740,13 +2785,13 @@
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>38</x:v>
@@ -2760,10 +2805,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>38</x:v>
@@ -2777,10 +2822,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>38</x:v>
@@ -2797,7 +2842,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>38</x:v>
@@ -2811,10 +2856,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>38</x:v>
@@ -2825,13 +2870,13 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>38</x:v>
@@ -2842,13 +2887,13 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>38</x:v>
@@ -2859,36 +2904,36 @@
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
@@ -2896,10 +2941,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>43</x:v>
@@ -2910,13 +2955,13 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>43</x:v>
@@ -2927,13 +2972,13 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>43</x:v>
@@ -2944,70 +2989,70 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
@@ -3015,10 +3060,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>50</x:v>
@@ -3032,10 +3077,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>50</x:v>
@@ -3049,10 +3094,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>50</x:v>
@@ -3066,10 +3111,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>50</x:v>
@@ -3083,13 +3128,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
         <x:v>51</x:v>
@@ -3097,16 +3142,16 @@
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
         <x:v>51</x:v>
@@ -3114,16 +3159,16 @@
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
         <x:v>51</x:v>
@@ -3134,13 +3179,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
         <x:v>51</x:v>
@@ -3148,16 +3193,16 @@
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
         <x:v>51</x:v>
@@ -3165,13 +3210,13 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>54</x:v>
@@ -3182,13 +3227,13 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>54</x:v>
@@ -3199,13 +3244,13 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>54</x:v>
@@ -3216,16 +3261,16 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
         <x:v>51</x:v>
@@ -3233,16 +3278,16 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
         <x:v>51</x:v>
@@ -3250,16 +3295,16 @@
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
         <x:v>51</x:v>
@@ -3267,16 +3312,16 @@
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
         <x:v>51</x:v>
@@ -3284,13 +3329,13 @@
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>59</x:v>
@@ -3301,13 +3346,13 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>59</x:v>
@@ -3324,7 +3369,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>59</x:v>
@@ -3338,10 +3383,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>59</x:v>
@@ -3355,10 +3400,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>59</x:v>
@@ -3372,10 +3417,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
         <x:v>59</x:v>
@@ -3386,16 +3431,16 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
         <x:v>51</x:v>
@@ -3403,16 +3448,16 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
         <x:v>51</x:v>
@@ -3420,13 +3465,13 @@
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>62</x:v>
@@ -3437,13 +3482,13 @@
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>62</x:v>
@@ -3454,597 +3499,716 @@
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D127" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B128" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C128" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D128" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B129" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C129" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D129" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C130" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D130" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C131" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D131" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C132" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D132" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B139" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C139" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D139" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B140" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C140" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D140" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C142" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D147" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B147" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C147" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D147" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D148" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C148" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D148" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C149" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D149" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B150" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C150" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D150" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C153" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D153" s="0" t="s">
+      <x:c r="E153" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="E153" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D154" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B154" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C154" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D154" s="0" t="s">
+      <x:c r="E154" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="E154" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E155" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="E155" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E156" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="E156" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E157" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="E157" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E158" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:11">
+      <x:c r="A159" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B158" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C158" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D158" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E158" s="0" t="s">
-        <x:v>81</x:v>
+      <x:c r="B159" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E159" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:11">
+      <x:c r="A160" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D160" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E160" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:11">
+      <x:c r="A161" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E161" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:11">
+      <x:c r="A162" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E162" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:11">
+      <x:c r="A163" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D163" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E163" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:11">
+      <x:c r="A164" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D164" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E164" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:11">
+      <x:c r="A165" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D165" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E165" s="0" t="s">
+        <x:v>84</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,234 +49,234 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.04.2026</x:t>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
   </x:si>
   <x:si>
     <x:t>12.05.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>MANAS</x:t>
   </x:si>
   <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
   </x:si>
   <x:si>
@@ -286,6 +286,27 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBRUT</x:t>
+  </x:si>
+  <x:si>
     <x:t>PASKI</x:t>
   </x:si>
   <x:si>
@@ -296,27 +317,6 @@
   </x:si>
   <x:si>
     <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PBRUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
   </x:si>
   <x:si>
     <x:t>16.04.2026</x:t>
@@ -734,10 +734,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
         <x:v>14</x:v>
@@ -751,28 +751,28 @@
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="A3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
         <x:v>14</x:v>
@@ -786,37 +786,37 @@
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
@@ -830,63 +830,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -900,138 +900,138 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>0</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>0</x:v>
+        <x:v>9.96</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="0">
         <x:v>0</x:v>
@@ -1040,33 +1040,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="0">
         <x:v>0</x:v>
@@ -1078,25 +1078,25 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
@@ -1113,16 +1113,16 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
         <x:v>14</x:v>
@@ -1145,63 +1145,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
@@ -1215,28 +1215,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
@@ -1256,22 +1256,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
@@ -1285,19 +1285,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
         <x:v>14</x:v>
@@ -1311,7 +1311,7 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1320,28 +1320,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
@@ -1358,130 +1358,130 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>0</x:v>
+        <x:v>259.75</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>0</x:v>
+        <x:v>5.8045</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -1495,19 +1495,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
         <x:v>14</x:v>
@@ -1521,72 +1521,72 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
@@ -1603,16 +1603,16 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
         <x:v>14</x:v>
@@ -1629,34 +1629,34 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>0</x:v>
+        <x:v>6.08</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
@@ -1664,74 +1664,74 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>0</x:v>
+        <x:v>32.62</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>0</x:v>
+        <x:v>9.98</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B31" s="0">
         <x:v>0</x:v>
@@ -1740,19 +1740,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
         <x:v>14</x:v>
@@ -1766,72 +1766,72 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
@@ -1845,63 +1845,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B35" s="0">
+        <x:v>7.38</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>2.36</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
+      <x:c r="E35" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
@@ -1915,28 +1915,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
@@ -1950,33 +1950,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B38" s="0">
         <x:v>0</x:v>
@@ -1985,7 +1985,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
         <x:v>80</x:v>
@@ -1994,54 +1994,54 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="B39" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
@@ -2055,33 +2055,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B41" s="0">
         <x:v>0</x:v>
@@ -2093,25 +2093,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
@@ -2128,25 +2128,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J42" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -2207,13 +2207,13 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>12</x:v>
@@ -2224,13 +2224,13 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>12</x:v>
@@ -2241,172 +2241,172 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D52" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E52" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E53" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E54" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D55" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E55" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
@@ -2414,16 +2414,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
@@ -2431,67 +2431,67 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D62" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E62" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D63" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E63" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
@@ -2499,237 +2499,237 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D66" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E69" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D69" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E69" s="0" t="s">
-        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E70" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D70" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E70" s="0" t="s">
-        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D72" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D73" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
@@ -2737,186 +2737,186 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E87" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="B87" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C87" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D87" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E87" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E88" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C88" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D88" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E88" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
@@ -2924,33 +2924,33 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
@@ -2958,10 +2958,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>43</x:v>
@@ -2975,10 +2975,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>43</x:v>
@@ -2998,10 +2998,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
@@ -3009,72 +3009,72 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D96" s="0" t="s">
+      <x:c r="E96" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="E96" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D97" s="0" t="s">
+      <x:c r="E97" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="E97" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>90</x:v>
@@ -3083,78 +3083,78 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -3162,135 +3162,135 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B108" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D108" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B109" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C109" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D109" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B110" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C110" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D110" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B111" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C111" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D111" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
@@ -3304,10 +3304,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
@@ -3315,169 +3315,169 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E120" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C120" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D120" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E120" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E121" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C121" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D121" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E121" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
@@ -3485,115 +3485,115 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
         <x:v>64</x:v>
@@ -3601,16 +3601,16 @@
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
         <x:v>64</x:v>
@@ -3618,16 +3618,16 @@
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
         <x:v>64</x:v>
@@ -3638,13 +3638,13 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
         <x:v>64</x:v>
@@ -3652,75 +3652,75 @@
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C134" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D134" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C135" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D135" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>90</x:v>
@@ -3729,83 +3729,83 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>92</x:v>
@@ -3814,15 +3814,15 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>97</x:v>
@@ -3831,61 +3831,61 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B145" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C145" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D145" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D146" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B146" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C146" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D146" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
@@ -3893,16 +3893,16 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
@@ -3910,50 +3910,50 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C149" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D149" s="0" t="s">
+      <x:c r="E149" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="E149" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B150" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C150" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D150" s="0" t="s">
+      <x:c r="E150" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="E150" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
@@ -3961,16 +3961,16 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E151" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="E151" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
@@ -3978,16 +3978,16 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E152" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="E152" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
@@ -3995,16 +3995,16 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
@@ -4012,30 +4012,30 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
         <x:v>80</x:v>
@@ -4043,16 +4043,16 @@
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
         <x:v>80</x:v>
@@ -4060,16 +4060,16 @@
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="B157" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C157" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D157" s="0" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
         <x:v>80</x:v>
@@ -4077,16 +4077,16 @@
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="B158" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C158" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D158" s="0" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
         <x:v>80</x:v>
@@ -4094,19 +4094,19 @@
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
@@ -4114,16 +4114,16 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
@@ -4131,50 +4131,50 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E161" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
@@ -4182,16 +4182,16 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E164" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
@@ -4199,16 +4199,16 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E165" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,234 +49,243 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>RNPOL</x:t>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
   </x:si>
   <x:si>
     <x:t>14.04.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
     <x:t>13.05.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
     <x:t>12.06.2026</x:t>
   </x:si>
   <x:si>
     <x:t>SURGY</x:t>
   </x:si>
   <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZERGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
   </x:si>
   <x:si>
@@ -286,37 +295,37 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PASKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açığa Satış Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKISY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kredili İşlem Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBRUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PPEGK</x:t>
   </x:si>
   <x:si>
     <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PBRUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKISY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kredili İşlem Yasağı</x:t>
   </x:si>
   <x:si>
     <x:t>16.04.2026</x:t>
@@ -676,7 +685,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K165"/>
+  <x:dimension ref="A1:K171"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -760,13 +769,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>14</x:v>
@@ -775,18 +784,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="0">
         <x:v>0</x:v>
@@ -795,13 +804,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>14</x:v>
@@ -810,33 +819,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>14</x:v>
@@ -845,13 +854,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
@@ -868,10 +877,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
         <x:v>14</x:v>
@@ -880,33 +889,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B7" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="E7" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>14</x:v>
@@ -915,13 +924,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -929,19 +938,19 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>58.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>9.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
         <x:v>14</x:v>
@@ -950,18 +959,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -970,13 +979,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>14</x:v>
@@ -985,18 +994,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="0">
         <x:v>0</x:v>
@@ -1005,13 +1014,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
         <x:v>14</x:v>
@@ -1020,33 +1029,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>14</x:v>
@@ -1055,13 +1064,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
@@ -1075,13 +1084,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
         <x:v>14</x:v>
@@ -1090,18 +1099,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B13" s="0">
         <x:v>0</x:v>
@@ -1110,13 +1119,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>14</x:v>
@@ -1125,33 +1134,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>14</x:v>
@@ -1160,13 +1169,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
@@ -1180,13 +1189,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
         <x:v>14</x:v>
@@ -1195,33 +1204,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B16" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B16" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
         <x:v>14</x:v>
@@ -1230,13 +1239,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
@@ -1256,7 +1265,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
         <x:v>14</x:v>
@@ -1265,13 +1274,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
@@ -1288,7 +1297,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>14</x:v>
@@ -1300,33 +1309,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B19" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C19" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B19" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C19" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
         <x:v>14</x:v>
@@ -1335,13 +1344,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
@@ -1355,13 +1364,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
         <x:v>14</x:v>
@@ -1370,33 +1379,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B21" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C21" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B21" s="0">
-        <x:v>259.75</x:v>
-      </x:c>
-      <x:c r="C21" s="0">
-        <x:v>5.8045</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
         <x:v>14</x:v>
@@ -1405,13 +1414,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -1428,10 +1437,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
         <x:v>14</x:v>
@@ -1440,13 +1449,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
@@ -1460,13 +1469,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
         <x:v>14</x:v>
@@ -1475,33 +1484,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
         <x:v>14</x:v>
@@ -1510,13 +1519,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -1530,13 +1539,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
         <x:v>14</x:v>
@@ -1545,13 +1554,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -1565,10 +1574,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>14</x:v>
@@ -1580,13 +1589,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
@@ -1600,11 +1609,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -1615,13 +1624,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
@@ -1629,16 +1638,16 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>6.08</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>14</x:v>
@@ -1650,33 +1659,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B29" s="0">
-        <x:v>32.62</x:v>
-      </x:c>
-      <x:c r="C29" s="0">
-        <x:v>9.98</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
         <x:v>14</x:v>
@@ -1685,13 +1694,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
@@ -1705,13 +1714,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
         <x:v>14</x:v>
@@ -1720,33 +1729,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
         <x:v>14</x:v>
@@ -1755,13 +1764,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
@@ -1778,10 +1787,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
         <x:v>14</x:v>
@@ -1790,13 +1799,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
@@ -1810,13 +1819,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
         <x:v>14</x:v>
@@ -1825,33 +1834,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
         <x:v>14</x:v>
@@ -1860,33 +1869,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B35" s="0">
-        <x:v>7.38</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>2.36</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
         <x:v>14</x:v>
@@ -1895,18 +1904,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B36" s="0">
         <x:v>0</x:v>
@@ -1915,13 +1924,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
         <x:v>14</x:v>
@@ -1930,33 +1939,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
         <x:v>14</x:v>
@@ -1965,13 +1974,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
@@ -1985,13 +1994,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
         <x:v>14</x:v>
@@ -2000,13 +2009,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
@@ -2020,13 +2029,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
         <x:v>14</x:v>
@@ -2035,33 +2044,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B40" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C40" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
         <x:v>14</x:v>
@@ -2070,33 +2079,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="B41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
         <x:v>14</x:v>
@@ -2105,13 +2114,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
@@ -2128,10 +2137,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
         <x:v>14</x:v>
@@ -2140,86 +2149,140 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:11">
+      <x:c r="A43" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B43" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C43" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J43" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K43" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B44" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C44" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J44" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K44" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
+      <x:c r="B45" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C45" s="0">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:11">
-      <x:c r="A46" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J45" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K45" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
@@ -2227,10 +2290,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>12</x:v>
@@ -2244,10 +2307,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>12</x:v>
@@ -2261,10 +2324,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>12</x:v>
@@ -2275,53 +2338,53 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
@@ -2329,16 +2392,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
@@ -2346,50 +2409,50 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
@@ -2397,50 +2460,50 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D60" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E60" s="0" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D61" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E61" s="0" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
@@ -2448,16 +2511,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
@@ -2465,67 +2528,67 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D65" s="0" t="s">
+      <x:c r="E65" s="0" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="E65" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="E66" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
@@ -2533,16 +2596,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
@@ -2550,50 +2613,50 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
@@ -2601,84 +2664,84 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D73" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E74" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C74" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D74" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E74" s="0" t="s">
-        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E75" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C75" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D75" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E75" s="0" t="s">
-        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
@@ -2686,16 +2749,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
@@ -2703,16 +2766,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
@@ -2723,149 +2786,149 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C84" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E85" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C85" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D85" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E85" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C86" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D86" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E86" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
@@ -2873,16 +2936,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
@@ -2890,67 +2953,67 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D90" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E90" s="0" t="s">
-        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
@@ -2958,10 +3021,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>43</x:v>
@@ -2975,10 +3038,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>43</x:v>
@@ -2989,70 +3052,70 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
@@ -3060,16 +3123,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
@@ -3077,16 +3140,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
@@ -3094,67 +3157,67 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D101" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B102" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D102" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B103" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C103" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D103" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -3162,67 +3225,67 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B106" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C106" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D106" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
@@ -3230,33 +3293,33 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
@@ -3264,16 +3327,16 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
@@ -3281,118 +3344,118 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C113" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C115" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D115" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C116" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D116" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
@@ -3400,16 +3463,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E118" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="E118" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
@@ -3417,16 +3480,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E119" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="E119" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
@@ -3434,16 +3497,16 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
@@ -3451,16 +3514,16 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
@@ -3468,67 +3531,67 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
@@ -3536,16 +3599,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C126" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D126" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E126" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="E126" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
@@ -3553,16 +3616,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="E127" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
@@ -3570,16 +3633,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E128" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="E128" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
@@ -3587,16 +3650,16 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
@@ -3604,16 +3667,16 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
@@ -3621,67 +3684,67 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C132" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D132" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B133" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C133" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D133" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C134" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D134" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
@@ -3689,16 +3752,16 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
@@ -3706,118 +3769,118 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C138" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B140" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C140" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D140" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D141" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C141" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D141" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
@@ -3825,33 +3888,33 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
@@ -3859,118 +3922,118 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D147" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B147" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C147" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D147" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D148" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C148" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D148" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E149" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C149" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D149" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E149" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E150" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="B150" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C150" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D150" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E150" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
@@ -3978,50 +4041,50 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E153" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C153" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D153" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E153" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D154" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E154" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B154" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C154" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D154" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E154" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
@@ -4029,16 +4092,16 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
@@ -4046,33 +4109,33 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C157" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
@@ -4080,101 +4143,101 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D160" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B160" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C160" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D160" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="E160" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B161" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C161" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D161" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="E161" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E162" s="0" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="B162" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C162" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D162" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E162" s="0" t="s">
-        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
@@ -4182,33 +4245,135 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E164" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E165" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:11">
+      <x:c r="A166" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D166" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E166" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:11">
+      <x:c r="A167" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E167" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:11">
+      <x:c r="A168" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E168" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:11">
+      <x:c r="A169" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E169" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:11">
+      <x:c r="A170" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E170" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:11">
+      <x:c r="A171" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E171" s="0" t="s">
+        <x:v>84</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,234 +49,225 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>DOGUB</x:t>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
   </x:si>
   <x:si>
     <x:t>15.04.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>04.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
     <x:t>14.05.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
     <x:t>EGEPO</x:t>
   </x:si>
   <x:si>
@@ -310,25 +301,25 @@
     <x:t>PBRUT</x:t>
   </x:si>
   <x:si>
+    <x:t>16.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
     <x:t>PYAYN</x:t>
   </x:si>
   <x:si>
     <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.04.2026</x:t>
   </x:si>
   <x:si>
     <x:t>PTEKF</x:t>
@@ -685,7 +676,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K171"/>
+  <x:dimension ref="A1:K164"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -749,18 +740,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="A3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="0">
         <x:v>0</x:v>
@@ -769,13 +760,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>14</x:v>
@@ -784,18 +775,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="0">
         <x:v>0</x:v>
@@ -804,13 +795,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>14</x:v>
@@ -819,18 +810,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>0</x:v>
@@ -845,7 +836,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>14</x:v>
@@ -854,18 +845,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -874,13 +865,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
         <x:v>14</x:v>
@@ -889,13 +880,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -915,7 +906,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>14</x:v>
@@ -924,13 +915,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -944,13 +935,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
         <x:v>14</x:v>
@@ -959,18 +950,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -979,13 +970,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>14</x:v>
@@ -994,33 +985,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
         <x:v>14</x:v>
@@ -1029,33 +1020,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>14</x:v>
@@ -1064,33 +1055,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
         <x:v>14</x:v>
@@ -1099,18 +1090,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="0">
         <x:v>0</x:v>
@@ -1119,13 +1110,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>14</x:v>
@@ -1134,18 +1125,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="0">
         <x:v>0</x:v>
@@ -1154,13 +1145,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>14</x:v>
@@ -1169,18 +1160,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="0">
         <x:v>0</x:v>
@@ -1189,13 +1180,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
         <x:v>14</x:v>
@@ -1204,18 +1195,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B16" s="0">
         <x:v>0</x:v>
@@ -1224,13 +1215,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
         <x:v>14</x:v>
@@ -1239,18 +1230,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1259,13 +1250,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
         <x:v>14</x:v>
@@ -1274,13 +1265,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
@@ -1297,10 +1288,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>14</x:v>
@@ -1309,13 +1300,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
@@ -1329,13 +1320,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
         <x:v>14</x:v>
@@ -1344,33 +1335,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
         <x:v>14</x:v>
@@ -1379,13 +1370,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
@@ -1402,10 +1393,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
         <x:v>14</x:v>
@@ -1414,33 +1405,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
         <x:v>14</x:v>
@@ -1449,18 +1440,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B23" s="0">
         <x:v>0</x:v>
@@ -1469,10 +1460,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>14</x:v>
@@ -1484,18 +1475,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="0">
         <x:v>0</x:v>
@@ -1504,13 +1495,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
         <x:v>14</x:v>
@@ -1519,31 +1510,31 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -1554,18 +1545,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B26" s="0">
         <x:v>0</x:v>
@@ -1574,13 +1565,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
         <x:v>14</x:v>
@@ -1589,18 +1580,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B27" s="0">
         <x:v>0</x:v>
@@ -1609,13 +1600,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
         <x:v>14</x:v>
@@ -1624,18 +1615,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B28" s="0">
         <x:v>0</x:v>
@@ -1644,13 +1635,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
         <x:v>14</x:v>
@@ -1659,18 +1650,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B29" s="0">
         <x:v>0</x:v>
@@ -1679,13 +1670,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
         <x:v>14</x:v>
@@ -1694,18 +1685,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B30" s="0">
         <x:v>0</x:v>
@@ -1714,13 +1705,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
         <x:v>14</x:v>
@@ -1729,33 +1720,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
+      <x:c r="E31" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
         <x:v>14</x:v>
@@ -1764,18 +1755,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B32" s="0">
         <x:v>0</x:v>
@@ -1784,13 +1775,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
         <x:v>14</x:v>
@@ -1799,18 +1790,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B33" s="0">
         <x:v>0</x:v>
@@ -1819,13 +1810,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
         <x:v>14</x:v>
@@ -1834,33 +1825,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
         <x:v>14</x:v>
@@ -1869,18 +1860,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B35" s="0">
         <x:v>0</x:v>
@@ -1889,13 +1880,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
         <x:v>14</x:v>
@@ -1904,18 +1895,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B36" s="0">
         <x:v>0</x:v>
@@ -1924,13 +1915,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
         <x:v>14</x:v>
@@ -1939,33 +1930,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
         <x:v>14</x:v>
@@ -1974,18 +1965,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B38" s="0">
         <x:v>0</x:v>
@@ -1997,10 +1988,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
         <x:v>14</x:v>
@@ -2009,18 +2000,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B39" s="0">
         <x:v>0</x:v>
@@ -2029,13 +2020,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
         <x:v>14</x:v>
@@ -2044,18 +2035,18 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B40" s="0">
         <x:v>0</x:v>
@@ -2067,10 +2058,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
         <x:v>14</x:v>
@@ -2079,13 +2070,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
@@ -2102,10 +2093,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
         <x:v>14</x:v>
@@ -2114,13 +2105,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
@@ -2134,13 +2125,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
         <x:v>14</x:v>
@@ -2149,154 +2140,100 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J42" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:11">
-      <x:c r="A43" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B43" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C43" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F43" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G43" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H43" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I43" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J43" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K43" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B44" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C44" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F44" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G44" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H44" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I44" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J44" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="K44" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B45" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C45" s="0">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="D45" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:11">
+      <x:c r="A46" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="E45" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G45" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H45" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I45" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J45" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="K45" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
         <x:v>13</x:v>
@@ -2304,16 +2241,16 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
         <x:v>13</x:v>
@@ -2321,234 +2258,234 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>24</x:v>
@@ -2559,13 +2496,13 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>24</x:v>
@@ -2576,16 +2513,16 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
         <x:v>25</x:v>
@@ -2593,16 +2530,16 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
         <x:v>25</x:v>
@@ -2610,19 +2547,19 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -2630,16 +2567,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
@@ -2647,123 +2584,123 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D72" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>100</x:v>
@@ -2772,126 +2709,126 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C79" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C82" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
         <x:v>37</x:v>
@@ -2899,16 +2836,16 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
         <x:v>37</x:v>
@@ -2916,16 +2853,16 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
         <x:v>37</x:v>
@@ -2933,16 +2870,16 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
         <x:v>37</x:v>
@@ -2950,16 +2887,16 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
         <x:v>37</x:v>
@@ -2967,1226 +2904,1226 @@
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E107" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="B107" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D107" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E107" s="0" t="s">
-        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E108" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="B108" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D108" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E108" s="0" t="s">
-        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B109" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C109" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D109" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C113" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C115" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E117" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C117" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D117" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E117" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E118" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C118" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D118" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E118" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E119" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C119" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D119" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E119" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C120" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D120" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C129" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C134" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C141" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D152" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E152" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="B152" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C152" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D152" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E152" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E153" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C153" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D153" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E153" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="C155" s="0" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C158" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
@@ -4194,16 +4131,16 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="C161" s="0" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="E161" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
@@ -4211,16 +4148,16 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
@@ -4228,16 +4165,16 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
@@ -4245,135 +4182,16 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E164" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165" spans="1:11">
-      <x:c r="A165" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B165" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C165" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D165" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E165" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166" spans="1:11">
-      <x:c r="A166" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C166" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D166" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E166" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" spans="1:11">
-      <x:c r="A167" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B167" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C167" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D167" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E167" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168" spans="1:11">
-      <x:c r="A168" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B168" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C168" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D168" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E168" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" spans="1:11">
-      <x:c r="A169" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B169" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C169" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D169" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E169" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" spans="1:11">
-      <x:c r="A170" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B170" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C170" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D170" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E170" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" spans="1:11">
-      <x:c r="A171" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B171" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C171" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D171" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E171" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,283 +49,274 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.04.2026</x:t>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZERGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Detaylı Kısıtlamalar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açıklama</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açığa Satış Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKISY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kredili İşlem Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBRUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PTEKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
   </x:si>
   <x:si>
     <x:t>15.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZERGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Detaylı Kısıtlamalar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açıklama</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKISY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PBRUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PTEKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
   </x:si>
 </x:sst>
 </file>
@@ -676,7 +667,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K164"/>
+  <x:dimension ref="A1:K163"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -734,19 +725,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -760,33 +751,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="0">
         <x:v>0</x:v>
@@ -795,33 +786,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>0</x:v>
@@ -836,27 +827,27 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -874,10 +865,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>15</x:v>
@@ -891,7 +882,7 @@
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="0">
         <x:v>0</x:v>
@@ -900,33 +891,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="0">
         <x:v>0</x:v>
@@ -944,16 +935,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
         <x:v>14</x:v>
@@ -961,7 +952,7 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -976,83 +967,83 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
+      <x:c r="E10" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
         <x:v>15</x:v>
@@ -1066,37 +1057,37 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
@@ -1113,16 +1104,16 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
         <x:v>14</x:v>
@@ -1136,7 +1127,7 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B14" s="0">
         <x:v>0</x:v>
@@ -1145,33 +1136,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B15" s="0">
         <x:v>0</x:v>
@@ -1180,33 +1171,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="0">
         <x:v>0</x:v>
@@ -1218,30 +1209,30 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1250,19 +1241,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
         <x:v>15</x:v>
@@ -1276,7 +1267,7 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B18" s="0">
         <x:v>0</x:v>
@@ -1285,33 +1276,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1323,16 +1314,16 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
         <x:v>14</x:v>
@@ -1358,16 +1349,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
         <x:v>15</x:v>
@@ -1396,22 +1387,22 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -1434,10 +1425,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
         <x:v>14</x:v>
@@ -1460,19 +1451,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
         <x:v>15</x:v>
@@ -1486,7 +1477,7 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B24" s="0">
         <x:v>0</x:v>
@@ -1495,33 +1486,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B25" s="0">
         <x:v>0</x:v>
@@ -1533,16 +1524,16 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
         <x:v>14</x:v>
@@ -1556,7 +1547,7 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B26" s="0">
         <x:v>0</x:v>
@@ -1565,68 +1556,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B28" s="0">
         <x:v>0</x:v>
@@ -1635,33 +1626,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B29" s="0">
         <x:v>0</x:v>
@@ -1670,33 +1661,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B30" s="0">
         <x:v>0</x:v>
@@ -1711,27 +1702,27 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B31" s="0">
         <x:v>0</x:v>
@@ -1746,48 +1737,48 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
         <x:v>15</x:v>
@@ -1801,7 +1792,7 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B33" s="0">
         <x:v>0</x:v>
@@ -1810,19 +1801,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
         <x:v>15</x:v>
@@ -1836,7 +1827,7 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B34" s="0">
         <x:v>0</x:v>
@@ -1848,30 +1839,30 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B35" s="0">
         <x:v>0</x:v>
@@ -1880,19 +1871,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
         <x:v>14</x:v>
@@ -1906,7 +1897,7 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B36" s="0">
         <x:v>0</x:v>
@@ -1915,19 +1906,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
         <x:v>14</x:v>
@@ -1941,7 +1932,7 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B37" s="0">
         <x:v>0</x:v>
@@ -1950,33 +1941,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B38" s="0">
         <x:v>0</x:v>
@@ -1985,33 +1976,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B39" s="0">
         <x:v>0</x:v>
@@ -2020,33 +2011,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B40" s="0">
         <x:v>0</x:v>
@@ -2055,25 +2046,25 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
         <x:v>15</x:v>
@@ -2081,7 +2072,7 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B41" s="0">
         <x:v>0</x:v>
@@ -2090,85 +2081,67 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:11">
-      <x:c r="A42" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B42" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C42" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F42" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G42" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H42" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I42" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J42" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K42" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:11">
+      <x:c r="A43" s="0" t="s">
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
@@ -2176,10 +2149,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>12</x:v>
@@ -2190,13 +2163,13 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>12</x:v>
@@ -2207,16 +2180,16 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
         <x:v>13</x:v>
@@ -2224,16 +2197,16 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
         <x:v>13</x:v>
@@ -2241,16 +2214,16 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
         <x:v>13</x:v>
@@ -2261,10 +2234,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>19</x:v>
@@ -2278,10 +2251,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>19</x:v>
@@ -2292,13 +2265,13 @@
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>19</x:v>
@@ -2312,10 +2285,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>19</x:v>
@@ -2326,13 +2299,13 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>19</x:v>
@@ -2343,13 +2316,13 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>19</x:v>
@@ -2360,41 +2333,41 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>96</x:v>
@@ -2403,55 +2376,55 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>24</x:v>
@@ -2462,13 +2435,13 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>24</x:v>
@@ -2479,13 +2452,13 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C64" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>24</x:v>
@@ -2499,10 +2472,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>24</x:v>
@@ -2513,13 +2486,13 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>24</x:v>
@@ -2533,140 +2506,140 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D68" s="0" t="s">
+      <x:c r="E68" s="0" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="E68" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D72" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E73" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D73" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E73" s="0" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E74" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C74" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D74" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E74" s="0" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>98</x:v>
@@ -2678,49 +2651,49 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>5</x:v>
@@ -2729,7 +2702,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
@@ -2737,16 +2710,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
@@ -2754,50 +2727,50 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
@@ -2805,16 +2778,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
@@ -2822,16 +2795,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
@@ -2839,16 +2812,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
@@ -2856,16 +2829,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
@@ -2873,16 +2846,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
@@ -2890,186 +2863,186 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C91" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C92" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E97" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D97" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E97" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E98" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D98" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E98" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
@@ -3077,16 +3050,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
@@ -3094,81 +3067,81 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
         <x:v>52</x:v>
@@ -3176,16 +3149,16 @@
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
         <x:v>52</x:v>
@@ -3193,13 +3166,13 @@
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>54</x:v>
@@ -3213,10 +3186,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>54</x:v>
@@ -3230,10 +3203,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>54</x:v>
@@ -3244,13 +3217,13 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>54</x:v>
@@ -3264,16 +3237,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
@@ -3281,16 +3254,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
@@ -3298,118 +3271,118 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
@@ -3417,16 +3390,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
@@ -3434,16 +3407,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
@@ -3451,16 +3424,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
@@ -3468,50 +3441,50 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C122" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E123" s="0" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="B123" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C123" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D123" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E123" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E124" s="0" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C124" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D124" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E124" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
@@ -3519,16 +3492,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
@@ -3536,16 +3509,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
@@ -3553,10 +3526,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>67</x:v>
@@ -3570,10 +3543,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>67</x:v>
@@ -3587,10 +3560,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>67</x:v>
@@ -3604,10 +3577,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>67</x:v>
@@ -3621,16 +3594,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
@@ -3638,288 +3611,288 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C132" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E133" s="0" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="B133" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C133" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D133" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E133" s="0" t="s">
-        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E134" s="0" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C134" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D134" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E134" s="0" t="s">
-        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E135" s="0" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C135" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D135" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E135" s="0" t="s">
-        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C138" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C142" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
@@ -3927,16 +3900,16 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
@@ -3944,16 +3917,16 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
@@ -3961,16 +3934,16 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
@@ -3978,16 +3951,16 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
@@ -3995,203 +3968,186 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C154" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D156" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E156" s="0" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="B156" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C156" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D156" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E156" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E157" s="0" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="B157" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C157" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D157" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E157" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E161" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C163" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164" spans="1:11">
-      <x:c r="A164" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B164" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C164" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D164" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E164" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,271 +49,262 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>ARZUM</x:t>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZERGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Detaylı Kısıtlamalar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açıklama</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açığa Satış Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKISY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kredili İşlem Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBRUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PTEKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
   </x:si>
   <x:si>
     <x:t>20.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZERGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Detaylı Kısıtlamalar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açıklama</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKISY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PBRUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PTEKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
   </x:si>
   <x:si>
     <x:t>15.05.2026</x:t>
@@ -667,7 +658,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K163"/>
+  <x:dimension ref="A1:K154"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -734,7 +725,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
         <x:v>14</x:v>
@@ -757,7 +748,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>15</x:v>
@@ -766,13 +757,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
@@ -862,7 +853,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
         <x:v>15</x:v>
@@ -871,13 +862,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -891,10 +882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>14</x:v>
@@ -917,7 +908,7 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="0">
         <x:v>0</x:v>
@@ -926,13 +917,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
         <x:v>15</x:v>
@@ -941,18 +932,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -961,13 +952,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>15</x:v>
@@ -987,19 +978,19 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="B10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>14</x:v>
@@ -1022,7 +1013,7 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="0">
         <x:v>0</x:v>
@@ -1034,10 +1025,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>15</x:v>
@@ -1046,13 +1037,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
@@ -1069,10 +1060,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
         <x:v>15</x:v>
@@ -1104,7 +1095,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>14</x:v>
@@ -1139,10 +1130,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>15</x:v>
@@ -1151,13 +1142,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
@@ -1174,7 +1165,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>14</x:v>
@@ -1209,10 +1200,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
         <x:v>15</x:v>
@@ -1232,19 +1223,19 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B17" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B17" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>32</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>15</x:v>
@@ -1267,7 +1258,7 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="0">
         <x:v>0</x:v>
@@ -1276,13 +1267,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>15</x:v>
@@ -1302,7 +1293,7 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1311,13 +1302,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
         <x:v>15</x:v>
@@ -1337,7 +1328,7 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B20" s="0">
         <x:v>0</x:v>
@@ -1372,7 +1363,7 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="0">
         <x:v>0</x:v>
@@ -1381,13 +1372,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
         <x:v>15</x:v>
@@ -1419,7 +1410,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>14</x:v>
@@ -1454,10 +1445,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
         <x:v>15</x:v>
@@ -1466,13 +1457,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -1489,7 +1480,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>14</x:v>
@@ -1512,19 +1503,19 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>14</x:v>
@@ -1556,10 +1547,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>14</x:v>
@@ -1661,13 +1652,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
         <x:v>15</x:v>
@@ -1676,33 +1667,33 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
         <x:v>15</x:v>
@@ -1711,30 +1702,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-   